--- a/research/traditional_assets/database/data/belgium/belgium_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_real_estate_general_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07283723357901184</v>
+        <v>0.07268889049506431</v>
       </c>
       <c r="C2">
-        <v>35.49581727349804</v>
+        <v>35.20117279718377</v>
       </c>
       <c r="D2">
-        <v>34.92781727349804</v>
+        <v>35.03489853518003</v>
       </c>
       <c r="E2">
-        <v>-24.87257379962572</v>
+        <v>-24.47084806162946</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4017257379962573</v>
       </c>
       <c r="G2">
         <v>0.5679999999999999</v>
@@ -1445,28 +1445,28 @@
         <v>2.8675</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02020680462121174</v>
       </c>
       <c r="N2">
-        <v>2.8675</v>
+        <v>2.847293195378788</v>
       </c>
       <c r="O2">
-        <v>0.7168749999999999</v>
+        <v>0.711823298844697</v>
       </c>
       <c r="P2">
-        <v>2.150625</v>
+        <v>2.135469896534091</v>
       </c>
       <c r="Q2">
-        <v>2.180625</v>
+        <v>2.165469896534091</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07283723357901184</v>
+        <v>0.07304206110612557</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5309984765800596</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>141.9076421904873</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07268889049506431</v>
+        <v>0.07254054741111679</v>
       </c>
       <c r="C3">
-        <v>35.20117279718377</v>
+        <v>34.9071869167475</v>
       </c>
       <c r="D3">
-        <v>35.03489853518003</v>
+        <v>35.14263839274002</v>
       </c>
       <c r="E3">
-        <v>-24.47084806162946</v>
+        <v>-24.06912232363321</v>
       </c>
       <c r="F3">
-        <v>0.4017257379962573</v>
+        <v>0.8034514759925145</v>
       </c>
       <c r="G3">
         <v>0.5679999999999999</v>
@@ -1527,28 +1527,28 @@
         <v>2.8675</v>
       </c>
       <c r="M3">
-        <v>0.02020680462121174</v>
+        <v>0.04041360924242348</v>
       </c>
       <c r="N3">
-        <v>2.847293195378788</v>
+        <v>2.827086390757576</v>
       </c>
       <c r="O3">
-        <v>0.711823298844697</v>
+        <v>0.706771597689394</v>
       </c>
       <c r="P3">
-        <v>2.135469896534091</v>
+        <v>2.120314793068182</v>
       </c>
       <c r="Q3">
-        <v>2.165469896534091</v>
+        <v>2.150314793068183</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07304206110612557</v>
+        <v>0.07325106878685386</v>
       </c>
       <c r="T3">
-        <v>0.5309984765800596</v>
+        <v>0.5350724253032456</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>141.9076421904873</v>
+        <v>70.95382109524361</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07254054741111679</v>
+        <v>0.07239220432716925</v>
       </c>
       <c r="C4">
-        <v>34.9071869167475</v>
+        <v>34.61386572690427</v>
       </c>
       <c r="D4">
-        <v>35.14263839274002</v>
+        <v>35.25104294089304</v>
       </c>
       <c r="E4">
-        <v>-24.06912232363321</v>
+        <v>-23.66739658563695</v>
       </c>
       <c r="F4">
-        <v>0.8034514759925145</v>
+        <v>1.205177213988772</v>
       </c>
       <c r="G4">
         <v>0.5679999999999999</v>
@@ -1609,28 +1609,28 @@
         <v>2.8675</v>
       </c>
       <c r="M4">
-        <v>0.04041360924242348</v>
+        <v>0.06062041386363522</v>
       </c>
       <c r="N4">
-        <v>2.827086390757576</v>
+        <v>2.806879586136365</v>
       </c>
       <c r="O4">
-        <v>0.706771597689394</v>
+        <v>0.7017198965340912</v>
       </c>
       <c r="P4">
-        <v>2.120314793068182</v>
+        <v>2.105159689602274</v>
       </c>
       <c r="Q4">
-        <v>2.150314793068183</v>
+        <v>2.135159689602274</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07325106878685386</v>
+        <v>0.0734643859042982</v>
       </c>
       <c r="T4">
-        <v>0.5350724253032456</v>
+        <v>0.5392303729691776</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.95382109524361</v>
+        <v>47.30254739682908</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07239220432716925</v>
+        <v>0.07224386124322173</v>
       </c>
       <c r="C5">
-        <v>34.61386572690427</v>
+        <v>34.32121539780326</v>
       </c>
       <c r="D5">
-        <v>35.25104294089304</v>
+        <v>35.36011834978829</v>
       </c>
       <c r="E5">
-        <v>-23.66739658563695</v>
+        <v>-23.26567084764069</v>
       </c>
       <c r="F5">
-        <v>1.205177213988772</v>
+        <v>1.606902951985029</v>
       </c>
       <c r="G5">
         <v>0.5679999999999999</v>
@@ -1691,28 +1691,28 @@
         <v>2.8675</v>
       </c>
       <c r="M5">
-        <v>0.06062041386363522</v>
+        <v>0.08082721848484696</v>
       </c>
       <c r="N5">
-        <v>2.806879586136365</v>
+        <v>2.786672781515153</v>
       </c>
       <c r="O5">
-        <v>0.7017198965340912</v>
+        <v>0.6966681953787882</v>
       </c>
       <c r="P5">
-        <v>2.105159689602274</v>
+        <v>2.090004586136365</v>
       </c>
       <c r="Q5">
-        <v>2.135159689602274</v>
+        <v>2.120004586136365</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0734643859042982</v>
+        <v>0.07368214712835597</v>
       </c>
       <c r="T5">
-        <v>0.5392303729691776</v>
+        <v>0.5434749445448166</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.30254739682908</v>
+        <v>35.47691054762181</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07224386124322173</v>
+        <v>0.0720955181592742</v>
       </c>
       <c r="C6">
-        <v>34.32121539780326</v>
+        <v>34.02924217619857</v>
       </c>
       <c r="D6">
-        <v>35.36011834978829</v>
+        <v>35.46987086617986</v>
       </c>
       <c r="E6">
-        <v>-23.26567084764069</v>
+        <v>-22.86394510964443</v>
       </c>
       <c r="F6">
-        <v>1.606902951985029</v>
+        <v>2.008628689981286</v>
       </c>
       <c r="G6">
         <v>0.5679999999999999</v>
@@ -1773,28 +1773,28 @@
         <v>2.8675</v>
       </c>
       <c r="M6">
-        <v>0.08082721848484696</v>
+        <v>0.1010340231060587</v>
       </c>
       <c r="N6">
-        <v>2.786672781515153</v>
+        <v>2.766465976893941</v>
       </c>
       <c r="O6">
-        <v>0.6966681953787882</v>
+        <v>0.6916164942234853</v>
       </c>
       <c r="P6">
-        <v>2.090004586136365</v>
+        <v>2.074849482670456</v>
       </c>
       <c r="Q6">
-        <v>2.120004586136365</v>
+        <v>2.104849482670456</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07368214712835597</v>
+        <v>0.073904492799236</v>
       </c>
       <c r="T6">
-        <v>0.5434749445448166</v>
+        <v>0.547808875522048</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.47691054762181</v>
+        <v>28.38152843809745</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0720955181592742</v>
+        <v>0.07194717507532666</v>
       </c>
       <c r="C7">
-        <v>34.02924217619857</v>
+        <v>33.73795238664173</v>
       </c>
       <c r="D7">
-        <v>35.46987086617986</v>
+        <v>35.58030681461928</v>
       </c>
       <c r="E7">
-        <v>-22.86394510964443</v>
+        <v>-22.46221937164817</v>
       </c>
       <c r="F7">
-        <v>2.008628689981286</v>
+        <v>2.410354427977544</v>
       </c>
       <c r="G7">
         <v>0.5679999999999999</v>
@@ -1855,28 +1855,28 @@
         <v>2.8675</v>
       </c>
       <c r="M7">
-        <v>0.1010340231060587</v>
+        <v>0.1212408277272704</v>
       </c>
       <c r="N7">
-        <v>2.766465976893941</v>
+        <v>2.746259172272729</v>
       </c>
       <c r="O7">
-        <v>0.6916164942234853</v>
+        <v>0.6865647930681823</v>
       </c>
       <c r="P7">
-        <v>2.074849482670456</v>
+        <v>2.059694379204547</v>
       </c>
       <c r="Q7">
-        <v>2.104849482670456</v>
+        <v>2.089694379204547</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.073904492799236</v>
+        <v>0.07413156922907092</v>
       </c>
       <c r="T7">
-        <v>0.547808875522048</v>
+        <v>0.5522350177966673</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.38152843809745</v>
+        <v>23.65127369841454</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07194717507532666</v>
+        <v>0.07179883199137914</v>
       </c>
       <c r="C8">
-        <v>33.73795238664173</v>
+        <v>33.44735243269656</v>
       </c>
       <c r="D8">
-        <v>35.58030681461928</v>
+        <v>35.69143259867037</v>
       </c>
       <c r="E8">
-        <v>-22.46221937164817</v>
+        <v>-22.06049363365192</v>
       </c>
       <c r="F8">
-        <v>2.410354427977544</v>
+        <v>2.8120801659738</v>
       </c>
       <c r="G8">
         <v>0.5679999999999999</v>
@@ -1937,28 +1937,28 @@
         <v>2.8675</v>
       </c>
       <c r="M8">
-        <v>0.1212408277272704</v>
+        <v>0.1414476323484821</v>
       </c>
       <c r="N8">
-        <v>2.746259172272729</v>
+        <v>2.726052367651517</v>
       </c>
       <c r="O8">
-        <v>0.6865647930681823</v>
+        <v>0.6815130919128793</v>
       </c>
       <c r="P8">
-        <v>2.059694379204547</v>
+        <v>2.044539275738638</v>
       </c>
       <c r="Q8">
-        <v>2.089694379204547</v>
+        <v>2.074539275738638</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07413156922907092</v>
+        <v>0.07436352902298832</v>
       </c>
       <c r="T8">
-        <v>0.5522350177966673</v>
+        <v>0.5567563459266548</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.65127369841454</v>
+        <v>20.27252031292675</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07179883199137913</v>
+        <v>0.07165048890743161</v>
       </c>
       <c r="C9">
-        <v>33.44735243269658</v>
+        <v>33.15744879817701</v>
       </c>
       <c r="D9">
-        <v>35.69143259867038</v>
+        <v>35.80325470214707</v>
       </c>
       <c r="E9">
-        <v>-22.06049363365192</v>
+        <v>-21.65876789565566</v>
       </c>
       <c r="F9">
-        <v>2.812080165973801</v>
+        <v>3.213805903970058</v>
       </c>
       <c r="G9">
         <v>0.5679999999999999</v>
@@ -2019,28 +2019,28 @@
         <v>2.8675</v>
       </c>
       <c r="M9">
-        <v>0.1414476323484822</v>
+        <v>0.1616544369696939</v>
       </c>
       <c r="N9">
-        <v>2.726052367651517</v>
+        <v>2.705845563030306</v>
       </c>
       <c r="O9">
-        <v>0.6815130919128793</v>
+        <v>0.6764613907575765</v>
       </c>
       <c r="P9">
-        <v>2.044539275738638</v>
+        <v>2.02938417227273</v>
       </c>
       <c r="Q9">
-        <v>2.074539275738638</v>
+        <v>2.05938417227273</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07436352902298832</v>
+        <v>0.07460053142112132</v>
       </c>
       <c r="T9">
-        <v>0.5567563459266548</v>
+        <v>0.5613759637985986</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.27252031292675</v>
+        <v>17.73845527381091</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07165048890743161</v>
+        <v>0.07150214582348408</v>
       </c>
       <c r="C10">
-        <v>33.15744879817701</v>
+        <v>32.86824804840814</v>
       </c>
       <c r="D10">
-        <v>35.80325470214707</v>
+        <v>35.91577969037446</v>
       </c>
       <c r="E10">
-        <v>-21.65876789565566</v>
+        <v>-21.25704215765941</v>
       </c>
       <c r="F10">
-        <v>3.213805903970058</v>
+        <v>3.615531641966315</v>
       </c>
       <c r="G10">
         <v>0.5679999999999999</v>
@@ -2101,28 +2101,28 @@
         <v>2.8675</v>
       </c>
       <c r="M10">
-        <v>0.1616544369696939</v>
+        <v>0.1818612415909056</v>
       </c>
       <c r="N10">
-        <v>2.705845563030306</v>
+        <v>2.685638758409094</v>
       </c>
       <c r="O10">
-        <v>0.6764613907575765</v>
+        <v>0.6714096896022735</v>
       </c>
       <c r="P10">
-        <v>2.02938417227273</v>
+        <v>2.014229068806821</v>
       </c>
       <c r="Q10">
-        <v>2.05938417227273</v>
+        <v>2.044229068806821</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07460053142112132</v>
+        <v>0.07484274266316931</v>
       </c>
       <c r="T10">
-        <v>0.5613759637985986</v>
+        <v>0.5660971117336618</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.73845527381091</v>
+        <v>15.76751579894303</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07150214582348408</v>
+        <v>0.07135380273953654</v>
       </c>
       <c r="C11">
-        <v>32.86824804840814</v>
+        <v>32.57975683151108</v>
       </c>
       <c r="D11">
-        <v>35.91577969037446</v>
+        <v>36.02901421147366</v>
       </c>
       <c r="E11">
-        <v>-21.25704215765941</v>
+        <v>-20.85531641966315</v>
       </c>
       <c r="F11">
-        <v>3.615531641966315</v>
+        <v>4.017257379962572</v>
       </c>
       <c r="G11">
         <v>0.5679999999999999</v>
@@ -2183,28 +2183,28 @@
         <v>2.8675</v>
       </c>
       <c r="M11">
-        <v>0.1818612415909056</v>
+        <v>0.2020680462121174</v>
       </c>
       <c r="N11">
-        <v>2.685638758409094</v>
+        <v>2.665431953787882</v>
       </c>
       <c r="O11">
-        <v>0.6714096896022735</v>
+        <v>0.6663579884469706</v>
       </c>
       <c r="P11">
-        <v>2.014229068806821</v>
+        <v>1.999073965340912</v>
       </c>
       <c r="Q11">
-        <v>2.044229068806821</v>
+        <v>2.029073965340912</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07484274266316931</v>
+        <v>0.07509033637726283</v>
       </c>
       <c r="T11">
-        <v>0.5660971117336618</v>
+        <v>0.5709231740672821</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.76751579894303</v>
+        <v>14.19076421904873</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07135380273953654</v>
+        <v>0.07120545965558901</v>
       </c>
       <c r="C12">
-        <v>32.57975683151108</v>
+        <v>32.29198187971237</v>
       </c>
       <c r="D12">
-        <v>36.02901421147366</v>
+        <v>36.14296499767121</v>
       </c>
       <c r="E12">
-        <v>-20.85531641966315</v>
+        <v>-20.45359068166689</v>
       </c>
       <c r="F12">
-        <v>4.017257379962572</v>
+        <v>4.418983117958829</v>
       </c>
       <c r="G12">
         <v>0.5679999999999999</v>
@@ -2265,28 +2265,28 @@
         <v>2.8675</v>
       </c>
       <c r="M12">
-        <v>0.2020680462121174</v>
+        <v>0.2222748508333291</v>
       </c>
       <c r="N12">
-        <v>2.665431953787882</v>
+        <v>2.645225149166671</v>
       </c>
       <c r="O12">
-        <v>0.6663579884469706</v>
+        <v>0.6613062872916676</v>
       </c>
       <c r="P12">
-        <v>1.999073965340912</v>
+        <v>1.983918861875003</v>
       </c>
       <c r="Q12">
-        <v>2.029073965340912</v>
+        <v>2.013918861875003</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07509033637726283</v>
+        <v>0.07534349399504384</v>
       </c>
       <c r="T12">
-        <v>0.5709231740672821</v>
+        <v>0.5758576872398602</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.19076421904873</v>
+        <v>12.90069474458975</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07120545965558901</v>
+        <v>0.07119211657164148</v>
       </c>
       <c r="C13">
-        <v>32.29198187971237</v>
+        <v>31.90054106850745</v>
       </c>
       <c r="D13">
-        <v>36.14296499767121</v>
+        <v>36.15324992446254</v>
       </c>
       <c r="E13">
-        <v>-20.45359068166689</v>
+        <v>-20.05186494367063</v>
       </c>
       <c r="F13">
-        <v>4.418983117958829</v>
+        <v>4.820708855955087</v>
       </c>
       <c r="G13">
         <v>0.5679999999999999</v>
@@ -2347,45 +2347,45 @@
         <v>2.8675</v>
       </c>
       <c r="M13">
-        <v>0.2222748508333291</v>
+        <v>0.2497127187384735</v>
       </c>
       <c r="N13">
-        <v>2.645225149166671</v>
+        <v>2.617787281261526</v>
       </c>
       <c r="O13">
-        <v>0.6613062872916676</v>
+        <v>0.6544468203153816</v>
       </c>
       <c r="P13">
-        <v>1.983918861875003</v>
+        <v>1.963340460946145</v>
       </c>
       <c r="Q13">
-        <v>2.013918861875003</v>
+        <v>1.993340460946145</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07534349399504384</v>
+        <v>0.07560240519504714</v>
       </c>
       <c r="T13">
-        <v>0.5758576872398602</v>
+        <v>0.5809043484390878</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.90069474458975</v>
+        <v>11.48319562770513</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07119211657164148</v>
+        <v>0.07105502348769395</v>
       </c>
       <c r="C14">
-        <v>31.90054106850745</v>
+        <v>31.60482749869288</v>
       </c>
       <c r="D14">
-        <v>36.15324992446254</v>
+        <v>36.25926209264423</v>
       </c>
       <c r="E14">
-        <v>-20.05186494367063</v>
+        <v>-19.65013920567437</v>
       </c>
       <c r="F14">
-        <v>4.820708855955087</v>
+        <v>5.222434593951344</v>
       </c>
       <c r="G14">
         <v>0.5679999999999999</v>
@@ -2429,28 +2429,28 @@
         <v>2.8675</v>
       </c>
       <c r="M14">
-        <v>0.2497127187384735</v>
+        <v>0.2705221119666796</v>
       </c>
       <c r="N14">
-        <v>2.617787281261526</v>
+        <v>2.59697788803332</v>
       </c>
       <c r="O14">
-        <v>0.6544468203153816</v>
+        <v>0.64924447200833</v>
       </c>
       <c r="P14">
-        <v>1.963340460946145</v>
+        <v>1.94773341602499</v>
       </c>
       <c r="Q14">
-        <v>1.993340460946145</v>
+        <v>1.97773341602499</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07560240519504714</v>
+        <v>0.07586726837665972</v>
       </c>
       <c r="T14">
-        <v>0.5809043484390878</v>
+        <v>0.5860670248382975</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.48319562770513</v>
+        <v>10.59987288711243</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07105502348769395</v>
+        <v>0.07091793040374643</v>
       </c>
       <c r="C15">
-        <v>31.60482749869288</v>
+        <v>31.30973747622906</v>
       </c>
       <c r="D15">
-        <v>36.25926209264423</v>
+        <v>36.36589780817666</v>
       </c>
       <c r="E15">
-        <v>-19.65013920567437</v>
+        <v>-19.24841346767812</v>
       </c>
       <c r="F15">
-        <v>5.222434593951344</v>
+        <v>5.624160331947602</v>
       </c>
       <c r="G15">
         <v>0.5679999999999999</v>
@@ -2511,28 +2511,28 @@
         <v>2.8675</v>
       </c>
       <c r="M15">
-        <v>0.2705221119666796</v>
+        <v>0.2913315051948858</v>
       </c>
       <c r="N15">
-        <v>2.59697788803332</v>
+        <v>2.576168494805114</v>
       </c>
       <c r="O15">
-        <v>0.64924447200833</v>
+        <v>0.6440421237012784</v>
       </c>
       <c r="P15">
-        <v>1.94773341602499</v>
+        <v>1.932126371103835</v>
       </c>
       <c r="Q15">
-        <v>1.97773341602499</v>
+        <v>1.962126371103836</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07586726837665972</v>
+        <v>0.07613829116714702</v>
       </c>
       <c r="T15">
-        <v>0.5860670248382975</v>
+        <v>0.5913497634793494</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.59987288711243</v>
+        <v>9.842739109461538</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07091793040374643</v>
+        <v>0.0709720873197989</v>
       </c>
       <c r="C16">
-        <v>31.30973747622906</v>
+        <v>30.86581176653926</v>
       </c>
       <c r="D16">
-        <v>36.36589780817666</v>
+        <v>36.32369783648312</v>
       </c>
       <c r="E16">
-        <v>-19.24841346767812</v>
+        <v>-18.84668772968186</v>
       </c>
       <c r="F16">
-        <v>5.624160331947602</v>
+        <v>6.025886069943859</v>
       </c>
       <c r="G16">
         <v>0.5679999999999999</v>
@@ -2593,45 +2593,45 @@
         <v>2.8675</v>
       </c>
       <c r="M16">
-        <v>0.2913315051948858</v>
+        <v>0.3223849047419965</v>
       </c>
       <c r="N16">
-        <v>2.576168494805114</v>
+        <v>2.545115095258003</v>
       </c>
       <c r="O16">
-        <v>0.6440421237012784</v>
+        <v>0.6362787738145008</v>
       </c>
       <c r="P16">
-        <v>1.932126371103835</v>
+        <v>1.908836321443502</v>
       </c>
       <c r="Q16">
-        <v>1.962126371103836</v>
+        <v>1.938836321443503</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07613829116714702</v>
+        <v>0.07641569096446929</v>
       </c>
       <c r="T16">
-        <v>0.5913497634793494</v>
+        <v>0.596756801853132</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.842739109461538</v>
+        <v>8.894647230132719</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0709720873197989</v>
+        <v>0.07084774423585137</v>
       </c>
       <c r="C17">
-        <v>30.86581176653926</v>
+        <v>30.56112233340657</v>
       </c>
       <c r="D17">
-        <v>36.32369783648312</v>
+        <v>36.42073414134669</v>
       </c>
       <c r="E17">
-        <v>-18.84668772968186</v>
+        <v>-18.4449619916856</v>
       </c>
       <c r="F17">
-        <v>6.025886069943859</v>
+        <v>6.427611807940116</v>
       </c>
       <c r="G17">
         <v>0.5679999999999999</v>
@@ -2675,28 +2675,28 @@
         <v>2.8675</v>
       </c>
       <c r="M17">
-        <v>0.3223849047419964</v>
+        <v>0.3438772317247962</v>
       </c>
       <c r="N17">
-        <v>2.545115095258003</v>
+        <v>2.523622768275203</v>
       </c>
       <c r="O17">
-        <v>0.6362787738145008</v>
+        <v>0.6309056920688009</v>
       </c>
       <c r="P17">
-        <v>1.908836321443502</v>
+        <v>1.892717076206403</v>
       </c>
       <c r="Q17">
-        <v>1.938836321443503</v>
+        <v>1.922717076206403</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07641569096446929</v>
+        <v>0.07669969551887068</v>
       </c>
       <c r="T17">
-        <v>0.596756801853132</v>
+        <v>0.6022925792358141</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.894647230132721</v>
+        <v>8.338731778249425</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07084774423585137</v>
+        <v>0.07072340115190384</v>
       </c>
       <c r="C18">
-        <v>30.56112233340657</v>
+        <v>30.25695274085888</v>
       </c>
       <c r="D18">
-        <v>36.42073414134669</v>
+        <v>36.51829028679526</v>
       </c>
       <c r="E18">
-        <v>-18.4449619916856</v>
+        <v>-18.04323625368935</v>
       </c>
       <c r="F18">
-        <v>6.427611807940116</v>
+        <v>6.829337545936373</v>
       </c>
       <c r="G18">
         <v>0.5679999999999999</v>
@@ -2757,28 +2757,28 @@
         <v>2.8675</v>
       </c>
       <c r="M18">
-        <v>0.3438772317247962</v>
+        <v>0.365369558707596</v>
       </c>
       <c r="N18">
-        <v>2.523622768275203</v>
+        <v>2.502130441292404</v>
       </c>
       <c r="O18">
-        <v>0.6309056920688009</v>
+        <v>0.6255326103231009</v>
       </c>
       <c r="P18">
-        <v>1.892717076206403</v>
+        <v>1.876597830969303</v>
       </c>
       <c r="Q18">
-        <v>1.922717076206403</v>
+        <v>1.906597830969303</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07669969551887068</v>
+        <v>0.07699054355651065</v>
       </c>
       <c r="T18">
-        <v>0.6022925792358141</v>
+        <v>0.607961748844585</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.338731778249425</v>
+        <v>7.848218144234753</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07072340115190384</v>
+        <v>0.07070705806795631</v>
       </c>
       <c r="C19">
-        <v>30.25695274085888</v>
+        <v>29.86808820830283</v>
       </c>
       <c r="D19">
-        <v>36.51829028679526</v>
+        <v>36.53115149223546</v>
       </c>
       <c r="E19">
-        <v>-18.04323625368935</v>
+        <v>-17.64151051569309</v>
       </c>
       <c r="F19">
-        <v>6.829337545936373</v>
+        <v>7.231063283932631</v>
       </c>
       <c r="G19">
         <v>0.5679999999999999</v>
@@ -2839,45 +2839,45 @@
         <v>2.8675</v>
       </c>
       <c r="M19">
-        <v>0.365369558707596</v>
+        <v>0.3926467363175419</v>
       </c>
       <c r="N19">
-        <v>2.502130441292404</v>
+        <v>2.474853263682458</v>
       </c>
       <c r="O19">
-        <v>0.6255326103231009</v>
+        <v>0.6187133159206144</v>
       </c>
       <c r="P19">
-        <v>1.876597830969303</v>
+        <v>1.856139947761843</v>
       </c>
       <c r="Q19">
-        <v>1.906597830969303</v>
+        <v>1.886139947761843</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07699054355651065</v>
+        <v>0.07728848544872721</v>
       </c>
       <c r="T19">
-        <v>0.607961748844585</v>
+        <v>0.613769190882838</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.848218144234753</v>
+        <v>7.303002253101603</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07070705806795632</v>
+        <v>0.07058871498400879</v>
       </c>
       <c r="C20">
-        <v>29.86808820830282</v>
+        <v>29.55976366669685</v>
       </c>
       <c r="D20">
-        <v>36.53115149223545</v>
+        <v>36.62455268862574</v>
       </c>
       <c r="E20">
-        <v>-17.64151051569309</v>
+        <v>-17.23978477769683</v>
       </c>
       <c r="F20">
-        <v>7.23106328393263</v>
+        <v>7.632789021928888</v>
       </c>
       <c r="G20">
         <v>0.5679999999999999</v>
@@ -2921,28 +2921,28 @@
         <v>2.8675</v>
       </c>
       <c r="M20">
-        <v>0.3926467363175418</v>
+        <v>0.4144604438907386</v>
       </c>
       <c r="N20">
-        <v>2.474853263682458</v>
+        <v>2.453039556109261</v>
       </c>
       <c r="O20">
-        <v>0.6187133159206145</v>
+        <v>0.6132598890273153</v>
       </c>
       <c r="P20">
-        <v>1.856139947761843</v>
+        <v>1.839779667081946</v>
       </c>
       <c r="Q20">
-        <v>1.886139947761844</v>
+        <v>1.869779667081946</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07728848544872721</v>
+        <v>0.07759378393087504</v>
       </c>
       <c r="T20">
-        <v>0.613769190882838</v>
+        <v>0.6197200265516652</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.303002253101606</v>
+        <v>6.918633713464678</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07058871498400879</v>
+        <v>0.07047037190006125</v>
       </c>
       <c r="C21">
-        <v>29.55976366669685</v>
+        <v>29.25191795725896</v>
       </c>
       <c r="D21">
-        <v>36.62455268862574</v>
+        <v>36.71843271718411</v>
       </c>
       <c r="E21">
-        <v>-17.23978477769683</v>
+        <v>-16.83805903970057</v>
       </c>
       <c r="F21">
-        <v>7.632789021928888</v>
+        <v>8.034514759925145</v>
       </c>
       <c r="G21">
         <v>0.5679999999999999</v>
@@ -3003,28 +3003,28 @@
         <v>2.8675</v>
       </c>
       <c r="M21">
-        <v>0.4144604438907386</v>
+        <v>0.4362741514639354</v>
       </c>
       <c r="N21">
-        <v>2.453039556109261</v>
+        <v>2.431225848536064</v>
       </c>
       <c r="O21">
-        <v>0.6132598890273153</v>
+        <v>0.6078064621340161</v>
       </c>
       <c r="P21">
-        <v>1.839779667081946</v>
+        <v>1.823419386402048</v>
       </c>
       <c r="Q21">
-        <v>1.869779667081946</v>
+        <v>1.853419386402049</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07759378393087504</v>
+        <v>0.07790671487507655</v>
       </c>
       <c r="T21">
-        <v>0.6197200265516652</v>
+        <v>0.6258196331122131</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.918633713464678</v>
+        <v>6.572702027791444</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07047037190006125</v>
+        <v>0.07035202881611373</v>
       </c>
       <c r="C22">
-        <v>29.25191795725896</v>
+        <v>28.94455477163573</v>
       </c>
       <c r="D22">
-        <v>36.71843271718411</v>
+        <v>36.81279526955714</v>
       </c>
       <c r="E22">
-        <v>-16.83805903970057</v>
+        <v>-16.43633330170432</v>
       </c>
       <c r="F22">
-        <v>8.034514759925145</v>
+        <v>8.436240497921403</v>
       </c>
       <c r="G22">
         <v>0.5679999999999999</v>
@@ -3085,28 +3085,28 @@
         <v>2.8675</v>
       </c>
       <c r="M22">
-        <v>0.4362741514639354</v>
+        <v>0.4580878590371322</v>
       </c>
       <c r="N22">
-        <v>2.431225848536064</v>
+        <v>2.409412140962868</v>
       </c>
       <c r="O22">
-        <v>0.6078064621340161</v>
+        <v>0.6023530352407169</v>
       </c>
       <c r="P22">
-        <v>1.823419386402048</v>
+        <v>1.807059105722151</v>
       </c>
       <c r="Q22">
-        <v>1.853419386402049</v>
+        <v>1.837059105722151</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07790671487507655</v>
+        <v>0.07822756812166294</v>
       </c>
       <c r="T22">
-        <v>0.6258196331122131</v>
+        <v>0.6320736600920154</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.572702027791444</v>
+        <v>6.259716216944232</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07035202881611373</v>
+        <v>0.07039868573216619</v>
       </c>
       <c r="C23">
-        <v>28.94455477163573</v>
+        <v>28.50556861858968</v>
       </c>
       <c r="D23">
-        <v>36.81279526955714</v>
+        <v>36.77553485450734</v>
       </c>
       <c r="E23">
-        <v>-16.43633330170432</v>
+        <v>-16.03460756370806</v>
       </c>
       <c r="F23">
-        <v>8.436240497921402</v>
+        <v>8.837966235917659</v>
       </c>
       <c r="G23">
         <v>0.5679999999999999</v>
@@ -3167,45 +3167,45 @@
         <v>2.8675</v>
       </c>
       <c r="M23">
-        <v>0.4580878590371321</v>
+        <v>0.4887395328462465</v>
       </c>
       <c r="N23">
-        <v>2.409412140962868</v>
+        <v>2.378760467153753</v>
       </c>
       <c r="O23">
-        <v>0.6023530352407169</v>
+        <v>0.5946901167884383</v>
       </c>
       <c r="P23">
-        <v>1.807059105722151</v>
+        <v>1.784070350365315</v>
       </c>
       <c r="Q23">
-        <v>1.837059105722151</v>
+        <v>1.814070350365315</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07822756812166294</v>
+        <v>0.07855664837457205</v>
       </c>
       <c r="T23">
-        <v>0.6320736600920154</v>
+        <v>0.6384880467379663</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.259716216944233</v>
+        <v>5.867133324166948</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07039868573216619</v>
+        <v>0.07028784264821866</v>
       </c>
       <c r="C24">
-        <v>28.50556861858968</v>
+        <v>28.19248620201015</v>
       </c>
       <c r="D24">
-        <v>36.77553485450734</v>
+        <v>36.86417817592407</v>
       </c>
       <c r="E24">
-        <v>-16.03460756370806</v>
+        <v>-15.6328818257118</v>
       </c>
       <c r="F24">
-        <v>8.837966235917659</v>
+        <v>9.239691973913917</v>
       </c>
       <c r="G24">
         <v>0.5679999999999999</v>
@@ -3249,28 +3249,28 @@
         <v>2.8675</v>
       </c>
       <c r="M24">
-        <v>0.4887395328462465</v>
+        <v>0.5109549661574396</v>
       </c>
       <c r="N24">
-        <v>2.378760467153753</v>
+        <v>2.35654503384256</v>
       </c>
       <c r="O24">
-        <v>0.5946901167884383</v>
+        <v>0.58913625846064</v>
       </c>
       <c r="P24">
-        <v>1.784070350365315</v>
+        <v>1.76740877538192</v>
       </c>
       <c r="Q24">
-        <v>1.814070350365315</v>
+        <v>1.79740877538192</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07855664837457205</v>
+        <v>0.07889427616651774</v>
       </c>
       <c r="T24">
-        <v>0.6384880467379663</v>
+        <v>0.6450690408292669</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.867133324166948</v>
+        <v>5.612040570942297</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07028784264821866</v>
+        <v>0.07017699956427113</v>
       </c>
       <c r="C25">
-        <v>28.19248620201015</v>
+        <v>27.87983214761143</v>
       </c>
       <c r="D25">
-        <v>36.86417817592407</v>
+        <v>36.95324985952161</v>
       </c>
       <c r="E25">
-        <v>-15.6328818257118</v>
+        <v>-15.23115608771555</v>
       </c>
       <c r="F25">
-        <v>9.239691973913917</v>
+        <v>9.641417711910174</v>
       </c>
       <c r="G25">
         <v>0.5679999999999999</v>
@@ -3331,28 +3331,28 @@
         <v>2.8675</v>
       </c>
       <c r="M25">
-        <v>0.5109549661574396</v>
+        <v>0.5331703994686326</v>
       </c>
       <c r="N25">
-        <v>2.35654503384256</v>
+        <v>2.334329600531367</v>
       </c>
       <c r="O25">
-        <v>0.58913625846064</v>
+        <v>0.5835824001328418</v>
       </c>
       <c r="P25">
-        <v>1.76740877538192</v>
+        <v>1.750747200398525</v>
       </c>
       <c r="Q25">
-        <v>1.79740877538192</v>
+        <v>1.780747200398526</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07889427616651774</v>
+        <v>0.07924078890035675</v>
       </c>
       <c r="T25">
-        <v>0.6450690408292669</v>
+        <v>0.6518232189756015</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.612040570942297</v>
+        <v>5.378205547153035</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07017699956427113</v>
+        <v>0.0700661564803236</v>
       </c>
       <c r="C26">
-        <v>27.87983214761143</v>
+        <v>27.56760956795611</v>
       </c>
       <c r="D26">
-        <v>36.95324985952161</v>
+        <v>37.04275301786254</v>
       </c>
       <c r="E26">
-        <v>-15.23115608771555</v>
+        <v>-14.82943034971929</v>
       </c>
       <c r="F26">
-        <v>9.641417711910174</v>
+        <v>10.04314344990643</v>
       </c>
       <c r="G26">
         <v>0.5679999999999999</v>
@@ -3413,28 +3413,28 @@
         <v>2.8675</v>
       </c>
       <c r="M26">
-        <v>0.5331703994686326</v>
+        <v>0.5553858327798257</v>
       </c>
       <c r="N26">
-        <v>2.334329600531367</v>
+        <v>2.312114167220174</v>
       </c>
       <c r="O26">
-        <v>0.5835824001328418</v>
+        <v>0.5780285418050435</v>
       </c>
       <c r="P26">
-        <v>1.750747200398525</v>
+        <v>1.73408562541513</v>
       </c>
       <c r="Q26">
-        <v>1.780747200398526</v>
+        <v>1.764085625415131</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07924078890035675</v>
+        <v>0.07959654197376481</v>
       </c>
       <c r="T26">
-        <v>0.6518232189756015</v>
+        <v>0.6587575085391717</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.378205547153035</v>
+        <v>5.163077325266913</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0700661564803236</v>
+        <v>0.06995531339637608</v>
       </c>
       <c r="C27">
-        <v>27.56760956795611</v>
+        <v>27.25582160583536</v>
       </c>
       <c r="D27">
-        <v>37.04275301786254</v>
+        <v>37.13269079373805</v>
       </c>
       <c r="E27">
-        <v>-14.82943034971929</v>
+        <v>-14.42770461172303</v>
       </c>
       <c r="F27">
-        <v>10.04314344990643</v>
+        <v>10.44486918790269</v>
       </c>
       <c r="G27">
         <v>0.5679999999999999</v>
@@ -3495,28 +3495,28 @@
         <v>2.8675</v>
       </c>
       <c r="M27">
-        <v>0.5553858327798257</v>
+        <v>0.5776012660910187</v>
       </c>
       <c r="N27">
-        <v>2.312114167220174</v>
+        <v>2.289898733908981</v>
       </c>
       <c r="O27">
-        <v>0.5780285418050435</v>
+        <v>0.5724746834772453</v>
       </c>
       <c r="P27">
-        <v>1.73408562541513</v>
+        <v>1.717424050431736</v>
       </c>
       <c r="Q27">
-        <v>1.764085625415131</v>
+        <v>1.747424050431736</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07959654197376481</v>
+        <v>0.0799619099951028</v>
       </c>
       <c r="T27">
-        <v>0.6587575085391717</v>
+        <v>0.6658792113341898</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.163077325266913</v>
+        <v>4.964497428141263</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06995531339637608</v>
+        <v>0.06984447031242855</v>
       </c>
       <c r="C28">
-        <v>27.25582160583536</v>
+        <v>26.9444714346367</v>
       </c>
       <c r="D28">
-        <v>37.13269079373805</v>
+        <v>37.22306636053565</v>
       </c>
       <c r="E28">
-        <v>-14.42770461172303</v>
+        <v>-14.02597887372677</v>
       </c>
       <c r="F28">
-        <v>10.44486918790269</v>
+        <v>10.84659492589895</v>
       </c>
       <c r="G28">
         <v>0.5679999999999999</v>
@@ -3577,28 +3577,28 @@
         <v>2.8675</v>
       </c>
       <c r="M28">
-        <v>0.5776012660910187</v>
+        <v>0.5998166994022117</v>
       </c>
       <c r="N28">
-        <v>2.289898733908981</v>
+        <v>2.267683300597788</v>
       </c>
       <c r="O28">
-        <v>0.5724746834772453</v>
+        <v>0.566920825149447</v>
       </c>
       <c r="P28">
-        <v>1.717424050431736</v>
+        <v>1.700762475448341</v>
       </c>
       <c r="Q28">
-        <v>1.747424050431736</v>
+        <v>1.730762475448341</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0799619099951028</v>
+        <v>0.0803372880992172</v>
       </c>
       <c r="T28">
-        <v>0.6658792113341898</v>
+        <v>0.6731960292742769</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.964497428141263</v>
+        <v>4.78062715302492</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06984447031242855</v>
+        <v>0.06973362722848102</v>
       </c>
       <c r="C29">
-        <v>26.9444714346367</v>
+        <v>26.63356225871731</v>
       </c>
       <c r="D29">
-        <v>37.22306636053565</v>
+        <v>37.31388292261251</v>
       </c>
       <c r="E29">
-        <v>-14.02597887372677</v>
+        <v>-13.62425313573052</v>
       </c>
       <c r="F29">
-        <v>10.84659492589895</v>
+        <v>11.2483206638952</v>
       </c>
       <c r="G29">
         <v>0.5679999999999999</v>
@@ -3659,28 +3659,28 @@
         <v>2.8675</v>
       </c>
       <c r="M29">
-        <v>0.5998166994022117</v>
+        <v>0.6220321327134047</v>
       </c>
       <c r="N29">
-        <v>2.267683300597788</v>
+        <v>2.245467867286595</v>
       </c>
       <c r="O29">
-        <v>0.566920825149447</v>
+        <v>0.5613669668216488</v>
       </c>
       <c r="P29">
-        <v>1.700762475448341</v>
+        <v>1.684100900464946</v>
       </c>
       <c r="Q29">
-        <v>1.730762475448341</v>
+        <v>1.714100900464947</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0803372880992172</v>
+        <v>0.0807230933728903</v>
       </c>
       <c r="T29">
-        <v>0.6731960292742769</v>
+        <v>0.6807160921571441</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.78062715302492</v>
+        <v>4.609890468988317</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06973362722848102</v>
+        <v>0.07016653414453349</v>
       </c>
       <c r="C30">
-        <v>26.63356225871731</v>
+        <v>25.87963554079247</v>
       </c>
       <c r="D30">
-        <v>37.31388292261251</v>
+        <v>36.96168194268394</v>
       </c>
       <c r="E30">
-        <v>-13.62425313573052</v>
+        <v>-13.22252739773426</v>
       </c>
       <c r="F30">
-        <v>11.2483206638952</v>
+        <v>11.65004640189146</v>
       </c>
       <c r="G30">
         <v>0.5679999999999999</v>
@@ -3741,45 +3741,45 @@
         <v>2.8675</v>
       </c>
       <c r="M30">
-        <v>0.6220321327134047</v>
+        <v>0.6733726820293265</v>
       </c>
       <c r="N30">
-        <v>2.245467867286595</v>
+        <v>2.194127317970673</v>
       </c>
       <c r="O30">
-        <v>0.5613669668216488</v>
+        <v>0.5485318294926683</v>
       </c>
       <c r="P30">
-        <v>1.684100900464946</v>
+        <v>1.645595488478005</v>
       </c>
       <c r="Q30">
-        <v>1.714100900464947</v>
+        <v>1.675595488478005</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0807230933728903</v>
+        <v>0.08111976640075139</v>
       </c>
       <c r="T30">
-        <v>0.6807160921571441</v>
+        <v>0.6884479877972751</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.609890468988317</v>
+        <v>4.258414510309931</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07016653414453347</v>
+        <v>0.07007444106058595</v>
       </c>
       <c r="C31">
-        <v>25.87963554079248</v>
+        <v>25.55227628720476</v>
       </c>
       <c r="D31">
-        <v>36.96168194268395</v>
+        <v>37.03604842709247</v>
       </c>
       <c r="E31">
-        <v>-13.22252739773426</v>
+        <v>-12.820801659738</v>
       </c>
       <c r="F31">
-        <v>11.65004640189146</v>
+        <v>12.05177213988772</v>
       </c>
       <c r="G31">
         <v>0.5679999999999999</v>
@@ -3823,28 +3823,28 @@
         <v>2.8675</v>
       </c>
       <c r="M31">
-        <v>0.6733726820293263</v>
+        <v>0.6965924296855101</v>
       </c>
       <c r="N31">
-        <v>2.194127317970673</v>
+        <v>2.17090757031449</v>
       </c>
       <c r="O31">
-        <v>0.5485318294926683</v>
+        <v>0.5427268925786224</v>
       </c>
       <c r="P31">
-        <v>1.645595488478005</v>
+        <v>1.628180677735867</v>
       </c>
       <c r="Q31">
-        <v>1.675595488478005</v>
+        <v>1.658180677735867</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08111976640075139</v>
+        <v>0.08152777294369422</v>
       </c>
       <c r="T31">
-        <v>0.6884479877972751</v>
+        <v>0.69640079474141</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.258414510309933</v>
+        <v>4.116467359966268</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07007444106058595</v>
+        <v>0.07079609797663843</v>
       </c>
       <c r="C32">
-        <v>25.55227628720476</v>
+        <v>24.57569313374399</v>
       </c>
       <c r="D32">
-        <v>37.03604842709247</v>
+        <v>36.46119101162797</v>
       </c>
       <c r="E32">
-        <v>-12.820801659738</v>
+        <v>-12.41907592174175</v>
       </c>
       <c r="F32">
-        <v>12.05177213988772</v>
+        <v>12.45349787788397</v>
       </c>
       <c r="G32">
         <v>0.5679999999999999</v>
@@ -3905,45 +3905,45 @@
         <v>2.8675</v>
       </c>
       <c r="M32">
-        <v>0.6965924296855101</v>
+        <v>0.7633994199142876</v>
       </c>
       <c r="N32">
-        <v>2.17090757031449</v>
+        <v>2.104100580085712</v>
       </c>
       <c r="O32">
-        <v>0.5427268925786224</v>
+        <v>0.5260251450214281</v>
       </c>
       <c r="P32">
-        <v>1.628180677735867</v>
+        <v>1.578075435064284</v>
       </c>
       <c r="Q32">
-        <v>1.658180677735867</v>
+        <v>1.608075435064285</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08152777294369422</v>
+        <v>0.0819476057632441</v>
       </c>
       <c r="T32">
-        <v>0.69640079474141</v>
+        <v>0.7045841178288532</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.116467359966268</v>
+        <v>3.756225018250544</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07079609797663843</v>
+        <v>0.07073025489269089</v>
       </c>
       <c r="C33">
-        <v>24.57569313374399</v>
+        <v>24.22567580787553</v>
       </c>
       <c r="D33">
-        <v>36.46119101162797</v>
+        <v>36.51289942375576</v>
       </c>
       <c r="E33">
-        <v>-12.41907592174175</v>
+        <v>-12.01735018374549</v>
       </c>
       <c r="F33">
-        <v>12.45349787788397</v>
+        <v>12.85522361588023</v>
       </c>
       <c r="G33">
         <v>0.5679999999999999</v>
@@ -3987,28 +3987,28 @@
         <v>2.8675</v>
       </c>
       <c r="M33">
-        <v>0.7633994199142876</v>
+        <v>0.7880252076534583</v>
       </c>
       <c r="N33">
-        <v>2.104100580085712</v>
+        <v>2.079474792346542</v>
       </c>
       <c r="O33">
-        <v>0.5260251450214281</v>
+        <v>0.5198686980866354</v>
       </c>
       <c r="P33">
-        <v>1.578075435064284</v>
+        <v>1.559606094259906</v>
       </c>
       <c r="Q33">
-        <v>1.608075435064285</v>
+        <v>1.589606094259906</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0819476057632441</v>
+        <v>0.08237978660689838</v>
       </c>
       <c r="T33">
-        <v>0.7045841178288532</v>
+        <v>0.7130081268894565</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.756225018250544</v>
+        <v>3.638842986430214</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07073025489269089</v>
+        <v>0.07066441180874337</v>
       </c>
       <c r="C34">
-        <v>24.22567580787553</v>
+        <v>23.87580535362916</v>
       </c>
       <c r="D34">
-        <v>36.51289942375576</v>
+        <v>36.56475470750565</v>
       </c>
       <c r="E34">
-        <v>-12.01735018374549</v>
+        <v>-11.61562444574923</v>
       </c>
       <c r="F34">
-        <v>12.85522361588023</v>
+        <v>13.25694935387649</v>
       </c>
       <c r="G34">
         <v>0.5679999999999999</v>
@@ -4069,28 +4069,28 @@
         <v>2.8675</v>
       </c>
       <c r="M34">
-        <v>0.7880252076534583</v>
+        <v>0.8126509953926289</v>
       </c>
       <c r="N34">
-        <v>2.079474792346542</v>
+        <v>2.054849004607371</v>
       </c>
       <c r="O34">
-        <v>0.5198686980866354</v>
+        <v>0.5137122511518427</v>
       </c>
       <c r="P34">
-        <v>1.559606094259906</v>
+        <v>1.541136753455528</v>
       </c>
       <c r="Q34">
-        <v>1.589606094259906</v>
+        <v>1.571136753455528</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08237978660689838</v>
+        <v>0.08282486837125877</v>
       </c>
       <c r="T34">
-        <v>0.7130081268894565</v>
+        <v>0.7216835989070927</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.638842986430214</v>
+        <v>3.52857501714445</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07066441180874337</v>
+        <v>0.07131256872479584</v>
       </c>
       <c r="C35">
-        <v>23.87580535362916</v>
+        <v>22.9699411518062</v>
       </c>
       <c r="D35">
-        <v>36.56475470750565</v>
+        <v>36.06061624367895</v>
       </c>
       <c r="E35">
-        <v>-11.61562444574923</v>
+        <v>-11.21389870775297</v>
       </c>
       <c r="F35">
-        <v>13.25694935387649</v>
+        <v>13.65867509187275</v>
       </c>
       <c r="G35">
         <v>0.5679999999999999</v>
@@ -4151,45 +4151,45 @@
         <v>2.8675</v>
       </c>
       <c r="M35">
-        <v>0.8126509953926289</v>
+        <v>0.8755210733890431</v>
       </c>
       <c r="N35">
-        <v>2.054849004607371</v>
+        <v>1.991978926610957</v>
       </c>
       <c r="O35">
-        <v>0.5137122511518427</v>
+        <v>0.4979947316527392</v>
       </c>
       <c r="P35">
-        <v>1.541136753455528</v>
+        <v>1.493984194958218</v>
       </c>
       <c r="Q35">
-        <v>1.571136753455528</v>
+        <v>1.523984194958218</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08282486837125877</v>
+        <v>0.08328343746181188</v>
       </c>
       <c r="T35">
-        <v>0.7216835989070927</v>
+        <v>0.7306219640161723</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.52857501714445</v>
+        <v>3.275192439286734</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07131256872479584</v>
+        <v>0.07126772564084831</v>
       </c>
       <c r="C36">
-        <v>22.9699411518062</v>
+        <v>22.60264645034341</v>
       </c>
       <c r="D36">
-        <v>36.06061624367895</v>
+        <v>36.09504728021242</v>
       </c>
       <c r="E36">
-        <v>-11.21389870775297</v>
+        <v>-10.81217296975671</v>
       </c>
       <c r="F36">
-        <v>13.65867509187275</v>
+        <v>14.06040082986901</v>
       </c>
       <c r="G36">
         <v>0.5679999999999999</v>
@@ -4233,28 +4233,28 @@
         <v>2.8675</v>
       </c>
       <c r="M36">
-        <v>0.8755210733890431</v>
+        <v>0.9012716931946033</v>
       </c>
       <c r="N36">
-        <v>1.991978926610957</v>
+        <v>1.966228306805396</v>
       </c>
       <c r="O36">
-        <v>0.4979947316527392</v>
+        <v>0.4915570767013491</v>
       </c>
       <c r="P36">
-        <v>1.493984194958218</v>
+        <v>1.474671230104047</v>
       </c>
       <c r="Q36">
-        <v>1.523984194958218</v>
+        <v>1.504671230104047</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08328343746181188</v>
+        <v>0.08375611637053586</v>
       </c>
       <c r="T36">
-        <v>0.7306219640161723</v>
+        <v>0.7398353557439928</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.275192439286734</v>
+        <v>3.181615512449969</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07126772564084831</v>
+        <v>0.07122288255690076</v>
       </c>
       <c r="C37">
-        <v>22.60264645034341</v>
+        <v>22.23541756191468</v>
       </c>
       <c r="D37">
-        <v>36.09504728021242</v>
+        <v>36.12954412977994</v>
       </c>
       <c r="E37">
-        <v>-10.81217296975671</v>
+        <v>-10.41044723176046</v>
       </c>
       <c r="F37">
-        <v>14.06040082986901</v>
+        <v>14.46212656786526</v>
       </c>
       <c r="G37">
         <v>0.5679999999999999</v>
@@ -4315,28 +4315,28 @@
         <v>2.8675</v>
       </c>
       <c r="M37">
-        <v>0.9012716931946033</v>
+        <v>0.9270223130001634</v>
       </c>
       <c r="N37">
-        <v>1.966228306805396</v>
+        <v>1.940477686999836</v>
       </c>
       <c r="O37">
-        <v>0.4915570767013491</v>
+        <v>0.4851194217499591</v>
       </c>
       <c r="P37">
-        <v>1.474671230104047</v>
+        <v>1.455358265249877</v>
       </c>
       <c r="Q37">
-        <v>1.504671230104047</v>
+        <v>1.485358265249878</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08375611637053586</v>
+        <v>0.08424356649515746</v>
       </c>
       <c r="T37">
-        <v>0.7398353557439928</v>
+        <v>0.7493366659633078</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.181615512449969</v>
+        <v>3.093237303770804</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07122288255690078</v>
+        <v>0.07117803947295324</v>
       </c>
       <c r="C38">
-        <v>22.23541756191467</v>
+        <v>21.86825467539748</v>
       </c>
       <c r="D38">
-        <v>36.12954412977994</v>
+        <v>36.164106981259</v>
       </c>
       <c r="E38">
-        <v>-10.41044723176046</v>
+        <v>-10.0087214937642</v>
       </c>
       <c r="F38">
-        <v>14.46212656786526</v>
+        <v>14.86385230586152</v>
       </c>
       <c r="G38">
         <v>0.5679999999999999</v>
@@ -4397,28 +4397,28 @@
         <v>2.8675</v>
       </c>
       <c r="M38">
-        <v>0.9270223130001632</v>
+        <v>0.9527729328057233</v>
       </c>
       <c r="N38">
-        <v>1.940477686999837</v>
+        <v>1.914727067194276</v>
       </c>
       <c r="O38">
-        <v>0.4851194217499591</v>
+        <v>0.4786817667985691</v>
       </c>
       <c r="P38">
-        <v>1.455358265249878</v>
+        <v>1.436045300395707</v>
       </c>
       <c r="Q38">
-        <v>1.485358265249878</v>
+        <v>1.466045300395708</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08424356649515746</v>
+        <v>0.08474649122690991</v>
       </c>
       <c r="T38">
-        <v>0.7493366659633078</v>
+        <v>0.759139605078474</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.093237303770805</v>
+        <v>3.009636295560783</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07117803947295324</v>
+        <v>0.07335619638900572</v>
       </c>
       <c r="C39">
-        <v>21.86825467539748</v>
+        <v>19.86072265133605</v>
       </c>
       <c r="D39">
-        <v>36.164106981259</v>
+        <v>34.55830069519383</v>
       </c>
       <c r="E39">
-        <v>-10.0087214937642</v>
+        <v>-9.606995755767944</v>
       </c>
       <c r="F39">
-        <v>14.86385230586152</v>
+        <v>15.26557804385778</v>
       </c>
       <c r="G39">
         <v>0.5679999999999999</v>
@@ -4479,45 +4479,45 @@
         <v>2.8675</v>
       </c>
       <c r="M39">
-        <v>0.9527729328057233</v>
+        <v>1.097595061353374</v>
       </c>
       <c r="N39">
-        <v>1.914727067194276</v>
+        <v>1.769904938646625</v>
       </c>
       <c r="O39">
-        <v>0.4786817667985691</v>
+        <v>0.4424762346616564</v>
       </c>
       <c r="P39">
-        <v>1.436045300395707</v>
+        <v>1.327428703984969</v>
       </c>
       <c r="Q39">
-        <v>1.466045300395708</v>
+        <v>1.357428703984969</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08474649122690991</v>
+        <v>0.085265639337106</v>
       </c>
       <c r="T39">
-        <v>0.759139605078474</v>
+        <v>0.7692587680360651</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.009636295560783</v>
+        <v>2.612529976642086</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07335619638900572</v>
+        <v>0.07336985330505819</v>
       </c>
       <c r="C40">
-        <v>19.86072265133605</v>
+        <v>19.44937834642883</v>
       </c>
       <c r="D40">
-        <v>34.55830069519383</v>
+        <v>34.54868212828286</v>
       </c>
       <c r="E40">
-        <v>-9.606995755767944</v>
+        <v>-9.205270017771687</v>
       </c>
       <c r="F40">
-        <v>15.26557804385778</v>
+        <v>15.66730378185403</v>
       </c>
       <c r="G40">
         <v>0.5679999999999999</v>
@@ -4561,28 +4561,28 @@
         <v>2.8675</v>
       </c>
       <c r="M40">
-        <v>1.097595061353374</v>
+        <v>1.126479141915305</v>
       </c>
       <c r="N40">
-        <v>1.769904938646625</v>
+        <v>1.741020858084695</v>
       </c>
       <c r="O40">
-        <v>0.4424762346616564</v>
+        <v>0.4352552145211737</v>
       </c>
       <c r="P40">
-        <v>1.327428703984969</v>
+        <v>1.305765643563521</v>
       </c>
       <c r="Q40">
-        <v>1.357428703984969</v>
+        <v>1.335765643563521</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.085265639337106</v>
+        <v>0.08580180869681669</v>
       </c>
       <c r="T40">
-        <v>0.7692587680360651</v>
+        <v>0.7797097068283311</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.612529976642086</v>
+        <v>2.545542028523058</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07336985330505819</v>
+        <v>0.07455351022111066</v>
       </c>
       <c r="C41">
-        <v>19.44937834642883</v>
+        <v>18.23386595968523</v>
       </c>
       <c r="D41">
-        <v>34.54868212828286</v>
+        <v>33.73489547953552</v>
       </c>
       <c r="E41">
-        <v>-9.205270017771687</v>
+        <v>-8.80354427977543</v>
       </c>
       <c r="F41">
-        <v>15.66730378185403</v>
+        <v>16.06902951985029</v>
       </c>
       <c r="G41">
         <v>0.5679999999999999</v>
@@ -4643,45 +4643,45 @@
         <v>2.8675</v>
       </c>
       <c r="M41">
-        <v>1.126479141915305</v>
+        <v>1.218032437604652</v>
       </c>
       <c r="N41">
-        <v>1.741020858084695</v>
+        <v>1.649467562395348</v>
       </c>
       <c r="O41">
-        <v>0.4352552145211737</v>
+        <v>0.4123668905988369</v>
       </c>
       <c r="P41">
-        <v>1.305765643563521</v>
+        <v>1.237100671796511</v>
       </c>
       <c r="Q41">
-        <v>1.335765643563521</v>
+        <v>1.267100671796511</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08580180869681669</v>
+        <v>0.08635585036851777</v>
       </c>
       <c r="T41">
-        <v>0.7797097068283311</v>
+        <v>0.790509010247006</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.545542028523058</v>
+        <v>2.354206597025563</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07455351022111066</v>
+        <v>0.07459641713716314</v>
       </c>
       <c r="C42">
-        <v>18.23386595968523</v>
+        <v>17.80336032431309</v>
       </c>
       <c r="D42">
-        <v>33.73489547953552</v>
+        <v>33.70611558215964</v>
       </c>
       <c r="E42">
-        <v>-8.80354427977543</v>
+        <v>-8.401818541779171</v>
       </c>
       <c r="F42">
-        <v>16.06902951985029</v>
+        <v>16.47075525784655</v>
       </c>
       <c r="G42">
         <v>0.5679999999999999</v>
@@ -4725,28 +4725,28 @@
         <v>2.8675</v>
       </c>
       <c r="M42">
-        <v>1.218032437604652</v>
+        <v>1.248483248544769</v>
       </c>
       <c r="N42">
-        <v>1.649467562395348</v>
+        <v>1.619016751455231</v>
       </c>
       <c r="O42">
-        <v>0.4123668905988369</v>
+        <v>0.4047541878638078</v>
       </c>
       <c r="P42">
-        <v>1.237100671796511</v>
+        <v>1.214262563591423</v>
       </c>
       <c r="Q42">
-        <v>1.267100671796511</v>
+        <v>1.244262563591424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08635585036851777</v>
+        <v>0.08692867311383581</v>
       </c>
       <c r="T42">
-        <v>0.790509010247006</v>
+        <v>0.8016743917476701</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.354206597025563</v>
+        <v>2.296786923927379</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07459641713716314</v>
+        <v>0.07463932405321561</v>
       </c>
       <c r="C43">
-        <v>17.80336032431309</v>
+        <v>17.37290375246759</v>
       </c>
       <c r="D43">
-        <v>33.70611558215964</v>
+        <v>33.6773847483104</v>
       </c>
       <c r="E43">
-        <v>-8.401818541779171</v>
+        <v>-8.000092803782913</v>
       </c>
       <c r="F43">
-        <v>16.47075525784655</v>
+        <v>16.87248099584281</v>
       </c>
       <c r="G43">
         <v>0.5679999999999999</v>
@@ -4807,28 +4807,28 @@
         <v>2.8675</v>
       </c>
       <c r="M43">
-        <v>1.248483248544769</v>
+        <v>1.278934059484885</v>
       </c>
       <c r="N43">
-        <v>1.619016751455231</v>
+        <v>1.588565940515115</v>
       </c>
       <c r="O43">
-        <v>0.4047541878638078</v>
+        <v>0.3971414851287787</v>
       </c>
       <c r="P43">
-        <v>1.214262563591423</v>
+        <v>1.191424455386336</v>
       </c>
       <c r="Q43">
-        <v>1.244262563591424</v>
+        <v>1.221424455386336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08692867311383581</v>
+        <v>0.0875212483676131</v>
       </c>
       <c r="T43">
-        <v>0.8016743917476701</v>
+        <v>0.8132247864035292</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.296786923927379</v>
+        <v>2.242101520976727</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07463932405321561</v>
+        <v>0.07468223096926807</v>
       </c>
       <c r="C44">
-        <v>17.3729037524676</v>
+        <v>16.94249611879146</v>
       </c>
       <c r="D44">
-        <v>33.6773847483104</v>
+        <v>33.64870285263053</v>
       </c>
       <c r="E44">
-        <v>-8.000092803782916</v>
+        <v>-7.598367065786658</v>
       </c>
       <c r="F44">
-        <v>16.8724809958428</v>
+        <v>17.27420673383906</v>
       </c>
       <c r="G44">
         <v>0.5679999999999999</v>
@@ -4889,28 +4889,28 @@
         <v>2.8675</v>
       </c>
       <c r="M44">
-        <v>1.278934059484885</v>
+        <v>1.309384870425001</v>
       </c>
       <c r="N44">
-        <v>1.588565940515115</v>
+        <v>1.558115129574999</v>
       </c>
       <c r="O44">
-        <v>0.3971414851287788</v>
+        <v>0.3895287823937497</v>
       </c>
       <c r="P44">
-        <v>1.191424455386336</v>
+        <v>1.168586347181249</v>
       </c>
       <c r="Q44">
-        <v>1.221424455386336</v>
+        <v>1.198586347181249</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0875212483676131</v>
+        <v>0.08813461573555802</v>
       </c>
       <c r="T44">
-        <v>0.8132247864035292</v>
+        <v>0.8251804580648571</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.242101520976727</v>
+        <v>2.189959625140059</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07468223096926807</v>
+        <v>0.07472513788532055</v>
       </c>
       <c r="C45">
-        <v>16.94249611879146</v>
+        <v>16.51213729835411</v>
       </c>
       <c r="D45">
-        <v>33.64870285263053</v>
+        <v>33.62006977018942</v>
       </c>
       <c r="E45">
-        <v>-7.598367065786658</v>
+        <v>-7.196641327790402</v>
       </c>
       <c r="F45">
-        <v>17.27420673383906</v>
+        <v>17.67593247183532</v>
       </c>
       <c r="G45">
         <v>0.5679999999999999</v>
@@ -4971,28 +4971,28 @@
         <v>2.8675</v>
       </c>
       <c r="M45">
-        <v>1.309384870425001</v>
+        <v>1.339835681365117</v>
       </c>
       <c r="N45">
-        <v>1.558115129574999</v>
+        <v>1.527664318634883</v>
       </c>
       <c r="O45">
-        <v>0.3895287823937497</v>
+        <v>0.3819160796587207</v>
       </c>
       <c r="P45">
-        <v>1.168586347181249</v>
+        <v>1.145748238976162</v>
       </c>
       <c r="Q45">
-        <v>1.198586347181249</v>
+        <v>1.175748238976162</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08813461573555802</v>
+        <v>0.08876988908092955</v>
       </c>
       <c r="T45">
-        <v>0.8251804580648571</v>
+        <v>0.8375631179998041</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.189959625140059</v>
+        <v>2.140187815477785</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07472513788532055</v>
+        <v>0.07476804480137302</v>
       </c>
       <c r="C46">
-        <v>16.51213729835411</v>
+        <v>16.08182716664984</v>
       </c>
       <c r="D46">
-        <v>33.62006977018942</v>
+        <v>33.59148537648142</v>
       </c>
       <c r="E46">
-        <v>-7.196641327790402</v>
+        <v>-6.794915589794144</v>
       </c>
       <c r="F46">
-        <v>17.67593247183532</v>
+        <v>18.07765820983158</v>
       </c>
       <c r="G46">
         <v>0.5679999999999999</v>
@@ -5053,28 +5053,28 @@
         <v>2.8675</v>
       </c>
       <c r="M46">
-        <v>1.339835681365117</v>
+        <v>1.370286492305234</v>
       </c>
       <c r="N46">
-        <v>1.527664318634883</v>
+        <v>1.497213507694766</v>
       </c>
       <c r="O46">
-        <v>0.3819160796587207</v>
+        <v>0.3743033769236915</v>
       </c>
       <c r="P46">
-        <v>1.145748238976162</v>
+        <v>1.122910130771074</v>
       </c>
       <c r="Q46">
-        <v>1.175748238976162</v>
+        <v>1.152910130771075</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08876988908092955</v>
+        <v>0.08942826327522366</v>
       </c>
       <c r="T46">
-        <v>0.8375631179998041</v>
+        <v>0.8503960564778398</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.140187815477785</v>
+        <v>2.092628086244945</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07476804480137302</v>
+        <v>0.07481095171742549</v>
       </c>
       <c r="C47">
-        <v>16.08182716664984</v>
+        <v>15.651565599596</v>
       </c>
       <c r="D47">
-        <v>33.59148537648142</v>
+        <v>33.56294954742383</v>
       </c>
       <c r="E47">
-        <v>-6.794915589794144</v>
+        <v>-6.393189851797885</v>
       </c>
       <c r="F47">
-        <v>18.07765820983158</v>
+        <v>18.47938394782783</v>
       </c>
       <c r="G47">
         <v>0.5679999999999999</v>
@@ -5135,28 +5135,28 @@
         <v>2.8675</v>
       </c>
       <c r="M47">
-        <v>1.370286492305234</v>
+        <v>1.40073730324535</v>
       </c>
       <c r="N47">
-        <v>1.497213507694766</v>
+        <v>1.46676269675465</v>
       </c>
       <c r="O47">
-        <v>0.3743033769236915</v>
+        <v>0.3666906741886624</v>
       </c>
       <c r="P47">
-        <v>1.122910130771074</v>
+        <v>1.100072022565987</v>
       </c>
       <c r="Q47">
-        <v>1.152910130771075</v>
+        <v>1.130072022565987</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08942826327522366</v>
+        <v>0.09011102169893608</v>
       </c>
       <c r="T47">
-        <v>0.8503960564778398</v>
+        <v>0.8637042889735806</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.092628086244945</v>
+        <v>2.047136171326577</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07481095171742549</v>
+        <v>0.07485385863347796</v>
       </c>
       <c r="C48">
-        <v>15.651565599596</v>
+        <v>15.22135247353124</v>
       </c>
       <c r="D48">
-        <v>33.56294954742383</v>
+        <v>33.53446215935534</v>
       </c>
       <c r="E48">
-        <v>-6.393189851797885</v>
+        <v>-5.991464113801626</v>
       </c>
       <c r="F48">
-        <v>18.47938394782783</v>
+        <v>18.88110968582409</v>
       </c>
       <c r="G48">
         <v>0.5679999999999999</v>
@@ -5217,28 +5217,28 @@
         <v>2.8675</v>
       </c>
       <c r="M48">
-        <v>1.40073730324535</v>
+        <v>1.431188114185466</v>
       </c>
       <c r="N48">
-        <v>1.46676269675465</v>
+        <v>1.436311885814533</v>
       </c>
       <c r="O48">
-        <v>0.3666906741886624</v>
+        <v>0.3590779714536333</v>
       </c>
       <c r="P48">
-        <v>1.100072022565987</v>
+        <v>1.0772339143609</v>
       </c>
       <c r="Q48">
-        <v>1.130072022565987</v>
+        <v>1.1072339143609</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09011102169893608</v>
+        <v>0.09081954459146784</v>
       </c>
       <c r="T48">
-        <v>0.8637042889735806</v>
+        <v>0.877514718921991</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.047136171326577</v>
+        <v>2.003580082574947</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07485385863347796</v>
+        <v>0.08000876554953043</v>
       </c>
       <c r="C49">
-        <v>15.22135247353124</v>
+        <v>11.71645113281772</v>
       </c>
       <c r="D49">
-        <v>33.53446215935534</v>
+        <v>30.43128655663807</v>
       </c>
       <c r="E49">
-        <v>-5.991464113801626</v>
+        <v>-5.589738375805371</v>
       </c>
       <c r="F49">
-        <v>18.88110968582409</v>
+        <v>19.28283542382035</v>
       </c>
       <c r="G49">
         <v>0.5679999999999999</v>
@@ -5299,45 +5299,45 @@
         <v>2.8675</v>
       </c>
       <c r="M49">
-        <v>1.431188114185466</v>
+        <v>1.735455188143831</v>
       </c>
       <c r="N49">
-        <v>1.436311885814533</v>
+        <v>1.132044811856168</v>
       </c>
       <c r="O49">
-        <v>0.3590779714536333</v>
+        <v>0.2830112029640421</v>
       </c>
       <c r="P49">
-        <v>1.0772339143609</v>
+        <v>0.8490336088921262</v>
       </c>
       <c r="Q49">
-        <v>1.1072339143609</v>
+        <v>0.8790336088921265</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09081954459146784</v>
+        <v>0.09155531836448158</v>
       </c>
       <c r="T49">
-        <v>0.877514718921991</v>
+        <v>0.8918563192530324</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.003580082574947</v>
+        <v>1.652304259764238</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08000876554953043</v>
+        <v>0.08015817246558289</v>
       </c>
       <c r="C50">
-        <v>11.71645113281772</v>
+        <v>11.23332585316848</v>
       </c>
       <c r="D50">
-        <v>30.43128655663807</v>
+        <v>30.34988701498508</v>
       </c>
       <c r="E50">
-        <v>-5.589738375805371</v>
+        <v>-5.188012637809116</v>
       </c>
       <c r="F50">
-        <v>19.28283542382035</v>
+        <v>19.6845611618166</v>
       </c>
       <c r="G50">
         <v>0.5679999999999999</v>
@@ -5381,28 +5381,28 @@
         <v>2.8675</v>
       </c>
       <c r="M50">
-        <v>1.735455188143831</v>
+        <v>1.771610504563494</v>
       </c>
       <c r="N50">
-        <v>1.132044811856168</v>
+        <v>1.095889495436505</v>
       </c>
       <c r="O50">
-        <v>0.2830112029640421</v>
+        <v>0.2739723738591264</v>
       </c>
       <c r="P50">
-        <v>0.8490336088921262</v>
+        <v>0.8219171215773791</v>
       </c>
       <c r="Q50">
-        <v>0.8790336088921265</v>
+        <v>0.8519171215773793</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09155531836448158</v>
+        <v>0.09231994601094684</v>
       </c>
       <c r="T50">
-        <v>0.8918563192530324</v>
+        <v>0.9067603352833304</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.652304259764238</v>
+        <v>1.618583764667009</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08015817246558289</v>
+        <v>0.08030757938163537</v>
       </c>
       <c r="C51">
-        <v>11.23332585316848</v>
+        <v>10.75063487716329</v>
       </c>
       <c r="D51">
-        <v>30.34988701498508</v>
+        <v>30.26892177697615</v>
       </c>
       <c r="E51">
-        <v>-5.188012637809116</v>
+        <v>-4.786286899812858</v>
       </c>
       <c r="F51">
-        <v>19.6845611618166</v>
+        <v>20.08628689981286</v>
       </c>
       <c r="G51">
         <v>0.5679999999999999</v>
@@ -5463,28 +5463,28 @@
         <v>2.8675</v>
       </c>
       <c r="M51">
-        <v>1.771610504563494</v>
+        <v>1.807765820983158</v>
       </c>
       <c r="N51">
-        <v>1.095889495436505</v>
+        <v>1.059734179016842</v>
       </c>
       <c r="O51">
-        <v>0.2739723738591264</v>
+        <v>0.2649335447542105</v>
       </c>
       <c r="P51">
-        <v>0.8219171215773791</v>
+        <v>0.7948006342626317</v>
       </c>
       <c r="Q51">
-        <v>0.8519171215773793</v>
+        <v>0.8248006342626319</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09231994601094684</v>
+        <v>0.09311515876327073</v>
       </c>
       <c r="T51">
-        <v>0.9067603352833304</v>
+        <v>0.9222605119548404</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.618583764667009</v>
+        <v>1.586212089373669</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08030757938163537</v>
+        <v>0.08045698629768784</v>
       </c>
       <c r="C52">
-        <v>10.75063487716329</v>
+        <v>10.26837473823826</v>
       </c>
       <c r="D52">
-        <v>30.26892177697615</v>
+        <v>30.18838737604738</v>
       </c>
       <c r="E52">
-        <v>-4.786286899812858</v>
+        <v>-4.384561161816599</v>
       </c>
       <c r="F52">
-        <v>20.08628689981286</v>
+        <v>20.48801263780912</v>
       </c>
       <c r="G52">
         <v>0.5679999999999999</v>
@@ -5545,28 +5545,28 @@
         <v>2.8675</v>
       </c>
       <c r="M52">
-        <v>1.807765820983158</v>
+        <v>1.843921137402821</v>
       </c>
       <c r="N52">
-        <v>1.059734179016842</v>
+        <v>1.023578862597179</v>
       </c>
       <c r="O52">
-        <v>0.2649335447542105</v>
+        <v>0.2558947156492947</v>
       </c>
       <c r="P52">
-        <v>0.7948006342626317</v>
+        <v>0.7676841469478841</v>
       </c>
       <c r="Q52">
-        <v>0.8248006342626319</v>
+        <v>0.7976841469478844</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09311515876327073</v>
+        <v>0.09394282917895477</v>
       </c>
       <c r="T52">
-        <v>0.9222605119548404</v>
+        <v>0.9383933488986569</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.586212089373669</v>
+        <v>1.555109891542812</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08045698629768784</v>
+        <v>0.0806063932137403</v>
       </c>
       <c r="C53">
-        <v>10.26837473823826</v>
+        <v>9.786542006624593</v>
       </c>
       <c r="D53">
-        <v>30.18838737604738</v>
+        <v>30.10828038242997</v>
       </c>
       <c r="E53">
-        <v>-4.384561161816599</v>
+        <v>-3.982835423820344</v>
       </c>
       <c r="F53">
-        <v>20.48801263780912</v>
+        <v>20.88973837580538</v>
       </c>
       <c r="G53">
         <v>0.5679999999999999</v>
@@ -5627,28 +5627,28 @@
         <v>2.8675</v>
       </c>
       <c r="M53">
-        <v>1.843921137402821</v>
+        <v>1.880076453822484</v>
       </c>
       <c r="N53">
-        <v>1.023578862597179</v>
+        <v>0.987423546177516</v>
       </c>
       <c r="O53">
-        <v>0.2558947156492947</v>
+        <v>0.246855886544379</v>
       </c>
       <c r="P53">
-        <v>0.7676841469478841</v>
+        <v>0.740567659633137</v>
       </c>
       <c r="Q53">
-        <v>0.7976841469478844</v>
+        <v>0.7705676596331372</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09394282917895477</v>
+        <v>0.09480498586195897</v>
       </c>
       <c r="T53">
-        <v>0.9383933488986569</v>
+        <v>0.955198387381799</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.555109891542812</v>
+        <v>1.525203932090066</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0806063932137403</v>
+        <v>0.1052357239283245</v>
       </c>
       <c r="C54">
-        <v>9.786542006624593</v>
+        <v>0.2223898623107452</v>
       </c>
       <c r="D54">
-        <v>30.10828038242997</v>
+        <v>20.94585397611238</v>
       </c>
       <c r="E54">
-        <v>-3.982835423820344</v>
+        <v>-3.581109685824085</v>
       </c>
       <c r="F54">
-        <v>20.88973837580538</v>
+        <v>21.29146411380163</v>
       </c>
       <c r="G54">
         <v>0.5679999999999999</v>
@@ -5709,45 +5709,45 @@
         <v>2.8675</v>
       </c>
       <c r="M54">
-        <v>1.880076453822484</v>
+        <v>3.12558693190608</v>
       </c>
       <c r="N54">
-        <v>0.987423546177516</v>
+        <v>-0.2580869319060803</v>
       </c>
       <c r="O54">
-        <v>0.246855886544379</v>
+        <v>-0.06452173297652009</v>
       </c>
       <c r="P54">
-        <v>0.740567659633137</v>
+        <v>-0.1935651989295603</v>
       </c>
       <c r="Q54">
-        <v>0.7705676596331372</v>
+        <v>-0.16356519892956</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09480498586195897</v>
+        <v>0.09633321262506009</v>
       </c>
       <c r="T54">
-        <v>0.955198387381799</v>
+        <v>0.9849863714816181</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.25</v>
+        <v>0.2293569225933599</v>
       </c>
       <c r="W54">
-        <v>0.0675</v>
+        <v>0.1131304037632948</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.525203932090066</v>
+        <v>0.9174276903734394</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1052357239283245</v>
+        <v>0.1062457239283245</v>
       </c>
       <c r="C55">
-        <v>0.2223898623107452</v>
+        <v>-0.4375055290660157</v>
       </c>
       <c r="D55">
-        <v>20.94585397611238</v>
+        <v>20.68768432273188</v>
       </c>
       <c r="E55">
-        <v>-3.581109685824085</v>
+        <v>-3.179383947827827</v>
       </c>
       <c r="F55">
-        <v>21.29146411380163</v>
+        <v>21.69318985179789</v>
       </c>
       <c r="G55">
         <v>0.5679999999999999</v>
@@ -5791,37 +5791,37 @@
         <v>2.8675</v>
       </c>
       <c r="M55">
-        <v>3.12558693190608</v>
+        <v>3.184560270243931</v>
       </c>
       <c r="N55">
-        <v>-0.2580869319060803</v>
+        <v>-0.3170602702439314</v>
       </c>
       <c r="O55">
-        <v>-0.06452173297652009</v>
+        <v>-0.07926506756098284</v>
       </c>
       <c r="P55">
-        <v>-0.1935651989295603</v>
+        <v>-0.2377952026829485</v>
       </c>
       <c r="Q55">
-        <v>-0.16356519892956</v>
+        <v>-0.2077952026829483</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09633321262506009</v>
+        <v>0.09743176072560486</v>
       </c>
       <c r="T55">
-        <v>0.9849863714816181</v>
+        <v>1.00639911868774</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2293569225933599</v>
+        <v>0.2251095721749643</v>
       </c>
       <c r="W55">
-        <v>0.1131304037632948</v>
+        <v>0.1137539148047153</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9174276903734394</v>
+        <v>0.9004382886998571</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1062457239283245</v>
+        <v>0.1072557239283245</v>
       </c>
       <c r="C56">
-        <v>-0.4375055290660157</v>
+        <v>-1.091114229662654</v>
       </c>
       <c r="D56">
-        <v>20.68768432273188</v>
+        <v>20.4358013601315</v>
       </c>
       <c r="E56">
-        <v>-3.179383947827827</v>
+        <v>-2.777658209831568</v>
       </c>
       <c r="F56">
-        <v>21.69318985179789</v>
+        <v>22.09491558979415</v>
       </c>
       <c r="G56">
         <v>0.5679999999999999</v>
@@ -5873,37 +5873,37 @@
         <v>2.8675</v>
       </c>
       <c r="M56">
-        <v>3.184560270243931</v>
+        <v>3.243533608581782</v>
       </c>
       <c r="N56">
-        <v>-0.3170602702439314</v>
+        <v>-0.3760336085817819</v>
       </c>
       <c r="O56">
-        <v>-0.07926506756098284</v>
+        <v>-0.09400840214544548</v>
       </c>
       <c r="P56">
-        <v>-0.2377952026829485</v>
+        <v>-0.2820252064363364</v>
       </c>
       <c r="Q56">
-        <v>-0.2077952026829483</v>
+        <v>-0.2520252064363362</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09743176072560486</v>
+        <v>0.09857913318617388</v>
       </c>
       <c r="T56">
-        <v>1.00639911868774</v>
+        <v>1.028763543547468</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2251095721749643</v>
+        <v>0.2210166708626922</v>
       </c>
       <c r="W56">
-        <v>0.1137539148047153</v>
+        <v>0.1143547527173568</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9004382886998571</v>
+        <v>0.8840666834507688</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1072557239283245</v>
+        <v>0.1082657239283245</v>
       </c>
       <c r="C57">
-        <v>-1.091114229662654</v>
+        <v>-1.738663108106909</v>
       </c>
       <c r="D57">
-        <v>20.4358013601315</v>
+        <v>20.1899782196835</v>
       </c>
       <c r="E57">
-        <v>-2.777658209831568</v>
+        <v>-2.375932471835313</v>
       </c>
       <c r="F57">
-        <v>22.09491558979415</v>
+        <v>22.49664132779041</v>
       </c>
       <c r="G57">
         <v>0.5679999999999999</v>
@@ -5955,37 +5955,37 @@
         <v>2.8675</v>
       </c>
       <c r="M57">
-        <v>3.243533608581782</v>
+        <v>3.302506946919632</v>
       </c>
       <c r="N57">
-        <v>-0.3760336085817819</v>
+        <v>-0.4350069469196325</v>
       </c>
       <c r="O57">
-        <v>-0.09400840214544548</v>
+        <v>-0.1087517367299081</v>
       </c>
       <c r="P57">
-        <v>-0.2820252064363364</v>
+        <v>-0.3262552101897244</v>
       </c>
       <c r="Q57">
-        <v>-0.2520252064363362</v>
+        <v>-0.2962552101897241</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09857913318617388</v>
+        <v>0.09977865894040509</v>
       </c>
       <c r="T57">
-        <v>1.028763543547468</v>
+        <v>1.052144533173547</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2210166708626922</v>
+        <v>0.217069944597287</v>
       </c>
       <c r="W57">
-        <v>0.1143547527173568</v>
+        <v>0.1149341321331183</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8840666834507688</v>
+        <v>0.8682797783891479</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1082657239283245</v>
+        <v>0.1092757239283245</v>
       </c>
       <c r="C58">
-        <v>-1.738663108106909</v>
+        <v>-2.380368246725226</v>
       </c>
       <c r="D58">
-        <v>20.1899782196835</v>
+        <v>19.94999881906144</v>
       </c>
       <c r="E58">
-        <v>-2.375932471835313</v>
+        <v>-1.974206733839054</v>
       </c>
       <c r="F58">
-        <v>22.49664132779041</v>
+        <v>22.89836706578667</v>
       </c>
       <c r="G58">
         <v>0.5679999999999999</v>
@@ -6037,37 +6037,37 @@
         <v>2.8675</v>
       </c>
       <c r="M58">
-        <v>3.302506946919632</v>
+        <v>3.361480285257483</v>
       </c>
       <c r="N58">
-        <v>-0.4350069469196325</v>
+        <v>-0.4939802852574831</v>
       </c>
       <c r="O58">
-        <v>-0.1087517367299081</v>
+        <v>-0.1234950713143708</v>
       </c>
       <c r="P58">
-        <v>-0.3262552101897244</v>
+        <v>-0.3704852139431123</v>
       </c>
       <c r="Q58">
-        <v>-0.2962552101897241</v>
+        <v>-0.340485213943112</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09977865894040509</v>
+        <v>0.101033976590182</v>
       </c>
       <c r="T58">
-        <v>1.052144533173547</v>
+        <v>1.076613010689211</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.217069944597287</v>
+        <v>0.2132616999552293</v>
       </c>
       <c r="W58">
-        <v>0.1149341321331183</v>
+        <v>0.1154931824465724</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8682797783891479</v>
+        <v>0.8530467998209172</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1092757239283245</v>
+        <v>0.1102857239283245</v>
       </c>
       <c r="C59">
-        <v>-2.380368246725226</v>
+        <v>-3.016435575046195</v>
       </c>
       <c r="D59">
-        <v>19.94999881906144</v>
+        <v>19.71565722873673</v>
       </c>
       <c r="E59">
-        <v>-1.974206733839054</v>
+        <v>-1.572480995842795</v>
       </c>
       <c r="F59">
-        <v>22.89836706578667</v>
+        <v>23.30009280378292</v>
       </c>
       <c r="G59">
         <v>0.5679999999999999</v>
@@ -6119,37 +6119,37 @@
         <v>2.8675</v>
       </c>
       <c r="M59">
-        <v>3.361480285257483</v>
+        <v>3.420453623595334</v>
       </c>
       <c r="N59">
-        <v>-0.4939802852574831</v>
+        <v>-0.5529536235953341</v>
       </c>
       <c r="O59">
-        <v>-0.1234950713143708</v>
+        <v>-0.1382384058988335</v>
       </c>
       <c r="P59">
-        <v>-0.3704852139431123</v>
+        <v>-0.4147152176965005</v>
       </c>
       <c r="Q59">
-        <v>-0.340485213943112</v>
+        <v>-0.3847152176965003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.101033976590182</v>
+        <v>0.1023490712709006</v>
       </c>
       <c r="T59">
-        <v>1.076613010689211</v>
+        <v>1.102246653800858</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2132616999552293</v>
+        <v>0.2095847740939322</v>
       </c>
       <c r="W59">
-        <v>0.1154931824465724</v>
+        <v>0.1160329551630108</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8530467998209172</v>
+        <v>0.8383390963757289</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1102857239283245</v>
+        <v>0.1112957239283245</v>
       </c>
       <c r="C60">
-        <v>-3.016435575046188</v>
+        <v>-3.64706145917409</v>
       </c>
       <c r="D60">
-        <v>19.71565722873673</v>
+        <v>19.48675708260508</v>
       </c>
       <c r="E60">
-        <v>-1.572480995842803</v>
+        <v>-1.170755257846544</v>
       </c>
       <c r="F60">
-        <v>23.30009280378292</v>
+        <v>23.70181854177918</v>
       </c>
       <c r="G60">
         <v>0.5679999999999999</v>
@@ -6201,37 +6201,37 @@
         <v>2.8675</v>
       </c>
       <c r="M60">
-        <v>3.420453623595332</v>
+        <v>3.479426961933183</v>
       </c>
       <c r="N60">
-        <v>-0.5529536235953327</v>
+        <v>-0.6119269619331837</v>
       </c>
       <c r="O60">
-        <v>-0.1382384058988332</v>
+        <v>-0.1529817404832959</v>
       </c>
       <c r="P60">
-        <v>-0.4147152176964995</v>
+        <v>-0.4589452214498878</v>
       </c>
       <c r="Q60">
-        <v>-0.3847152176964993</v>
+        <v>-0.4289452214498876</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1023490712709006</v>
+        <v>0.1037283169116542</v>
       </c>
       <c r="T60">
-        <v>1.102246653800858</v>
+        <v>1.129130718527708</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2095847740939323</v>
+        <v>0.2060324897872555</v>
       </c>
       <c r="W60">
-        <v>0.1160329551630108</v>
+        <v>0.1165544304992309</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8383390963757292</v>
+        <v>0.8241299591490219</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1112957239283245</v>
+        <v>0.1123057239283245</v>
       </c>
       <c r="C61">
-        <v>-3.64706145917409</v>
+        <v>-4.272433250577404</v>
       </c>
       <c r="D61">
-        <v>19.48675708260508</v>
+        <v>19.26311102919803</v>
       </c>
       <c r="E61">
-        <v>-1.170755257846544</v>
+        <v>-0.7690295198502852</v>
       </c>
       <c r="F61">
-        <v>23.70181854177918</v>
+        <v>24.10354427977543</v>
       </c>
       <c r="G61">
         <v>0.5679999999999999</v>
@@ -6283,37 +6283,37 @@
         <v>2.8675</v>
       </c>
       <c r="M61">
-        <v>3.479426961933183</v>
+        <v>3.538400300271034</v>
       </c>
       <c r="N61">
-        <v>-0.6119269619331837</v>
+        <v>-0.6709003002710343</v>
       </c>
       <c r="O61">
-        <v>-0.1529817404832959</v>
+        <v>-0.1677250750677586</v>
       </c>
       <c r="P61">
-        <v>-0.4589452214498878</v>
+        <v>-0.5031752252032757</v>
       </c>
       <c r="Q61">
-        <v>-0.4289452214498876</v>
+        <v>-0.4731752252032755</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1037283169116542</v>
+        <v>0.1051765248344456</v>
       </c>
       <c r="T61">
-        <v>1.129130718527708</v>
+        <v>1.157358986490901</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2060324897872555</v>
+        <v>0.2025986149574679</v>
       </c>
       <c r="W61">
-        <v>0.1165544304992309</v>
+        <v>0.1170585233242437</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8241299591490219</v>
+        <v>0.8103944598298715</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1123057239283245</v>
+        <v>0.1471395769006482</v>
       </c>
       <c r="C62">
-        <v>-4.272433250577404</v>
+        <v>-10.13673714676644</v>
       </c>
       <c r="D62">
-        <v>19.26311102919803</v>
+        <v>13.80053287100525</v>
       </c>
       <c r="E62">
-        <v>-0.7690295198502852</v>
+        <v>-0.3673037818540301</v>
       </c>
       <c r="F62">
-        <v>24.10354427977543</v>
+        <v>24.50527001777169</v>
       </c>
       <c r="G62">
         <v>0.5679999999999999</v>
@@ -6365,45 +6365,45 @@
         <v>2.8675</v>
       </c>
       <c r="M62">
-        <v>3.538400300271034</v>
+        <v>4.920658219568556</v>
       </c>
       <c r="N62">
-        <v>-0.6709003002710343</v>
+        <v>-2.053158219568556</v>
       </c>
       <c r="O62">
-        <v>-0.1677250750677586</v>
+        <v>-0.513289554892139</v>
       </c>
       <c r="P62">
-        <v>-0.5031752252032757</v>
+        <v>-1.539868664676417</v>
       </c>
       <c r="Q62">
-        <v>-0.4731752252032755</v>
+        <v>-1.509868664676417</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1051765248344456</v>
+        <v>0.1089652895028257</v>
       </c>
       <c r="T62">
-        <v>1.157358986490901</v>
+        <v>1.231209061901598</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.2025986149574679</v>
+        <v>0.1456868101810281</v>
       </c>
       <c r="W62">
-        <v>0.1170585233242437</v>
+        <v>0.1715460885156496</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8103944598298715</v>
+        <v>0.5827472407241124</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1471395769006482</v>
+        <v>0.1486895769006482</v>
       </c>
       <c r="C63">
-        <v>-10.13673714676644</v>
+        <v>-10.71043241180259</v>
       </c>
       <c r="D63">
-        <v>13.80053287100525</v>
+        <v>13.62856334396536</v>
       </c>
       <c r="E63">
-        <v>-0.3673037818540301</v>
+        <v>0.03442195614222854</v>
       </c>
       <c r="F63">
-        <v>24.50527001777169</v>
+        <v>24.90699575576795</v>
       </c>
       <c r="G63">
         <v>0.5679999999999999</v>
@@ -6447,37 +6447,37 @@
         <v>2.8675</v>
       </c>
       <c r="M63">
-        <v>4.920658219568556</v>
+        <v>5.001324747758204</v>
       </c>
       <c r="N63">
-        <v>-2.053158219568556</v>
+        <v>-2.133824747758204</v>
       </c>
       <c r="O63">
-        <v>-0.513289554892139</v>
+        <v>-0.5334561869395511</v>
       </c>
       <c r="P63">
-        <v>-1.539868664676417</v>
+        <v>-1.600368560818653</v>
       </c>
       <c r="Q63">
-        <v>-1.509868664676417</v>
+        <v>-1.570368560818653</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1089652895028257</v>
+        <v>0.1106275339634264</v>
       </c>
       <c r="T63">
-        <v>1.231209061901598</v>
+        <v>1.263609300372692</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1456868101810281</v>
+        <v>0.1433370229200438</v>
       </c>
       <c r="W63">
-        <v>0.1715460885156496</v>
+        <v>0.1720179257976552</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5827472407241124</v>
+        <v>0.5733480916801752</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1486895769006482</v>
+        <v>0.1502395769006483</v>
       </c>
       <c r="C64">
-        <v>-10.71043241180259</v>
+        <v>-11.27989457422222</v>
       </c>
       <c r="D64">
-        <v>13.62856334396536</v>
+        <v>13.46082691954199</v>
       </c>
       <c r="E64">
-        <v>0.03442195614222854</v>
+        <v>0.4361476941384872</v>
       </c>
       <c r="F64">
-        <v>24.90699575576795</v>
+        <v>25.30872149376421</v>
       </c>
       <c r="G64">
         <v>0.5679999999999999</v>
@@ -6529,37 +6529,37 @@
         <v>2.8675</v>
       </c>
       <c r="M64">
-        <v>5.001324747758204</v>
+        <v>5.081991275947852</v>
       </c>
       <c r="N64">
-        <v>-2.133824747758204</v>
+        <v>-2.214491275947853</v>
       </c>
       <c r="O64">
-        <v>-0.5334561869395511</v>
+        <v>-0.5536228189869632</v>
       </c>
       <c r="P64">
-        <v>-1.600368560818653</v>
+        <v>-1.66086845696089</v>
       </c>
       <c r="Q64">
-        <v>-1.570368560818653</v>
+        <v>-1.630868456960889</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1106275339634264</v>
+        <v>0.1123796294759514</v>
       </c>
       <c r="T64">
-        <v>1.263609300372692</v>
+        <v>1.297760903085468</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1433370229200438</v>
+        <v>0.1410618320800431</v>
       </c>
       <c r="W64">
-        <v>0.1720179257976552</v>
+        <v>0.1724747841183274</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5733480916801752</v>
+        <v>0.5642473283201723</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1502395769006483</v>
+        <v>0.1517895769006483</v>
       </c>
       <c r="C65">
-        <v>-11.27989457422222</v>
+        <v>-11.84527803314152</v>
       </c>
       <c r="D65">
-        <v>13.46082691954199</v>
+        <v>13.29716919861894</v>
       </c>
       <c r="E65">
-        <v>0.4361476941384872</v>
+        <v>0.8378734321347459</v>
       </c>
       <c r="F65">
-        <v>25.30872149376421</v>
+        <v>25.71044723176047</v>
       </c>
       <c r="G65">
         <v>0.5679999999999999</v>
@@ -6611,37 +6611,37 @@
         <v>2.8675</v>
       </c>
       <c r="M65">
-        <v>5.081991275947852</v>
+        <v>5.162657804137502</v>
       </c>
       <c r="N65">
-        <v>-2.214491275947853</v>
+        <v>-2.295157804137502</v>
       </c>
       <c r="O65">
-        <v>-0.5536228189869632</v>
+        <v>-0.5737894510343755</v>
       </c>
       <c r="P65">
-        <v>-1.66086845696089</v>
+        <v>-1.721368353103127</v>
       </c>
       <c r="Q65">
-        <v>-1.630868456960889</v>
+        <v>-1.691368353103126</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1123796294759514</v>
+        <v>0.1142290636280612</v>
       </c>
       <c r="T65">
-        <v>1.297760903085468</v>
+        <v>1.333809817060065</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1410618320800431</v>
+        <v>0.1388577409537924</v>
       </c>
       <c r="W65">
-        <v>0.1724747841183274</v>
+        <v>0.1729173656164785</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5642473283201723</v>
+        <v>0.5554309638151695</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1517895769006483</v>
+        <v>0.1533395769006483</v>
       </c>
       <c r="C66">
-        <v>-11.84527803314152</v>
+        <v>-12.40672976908935</v>
       </c>
       <c r="D66">
-        <v>13.29716919861894</v>
+        <v>13.13744320066737</v>
       </c>
       <c r="E66">
-        <v>0.8378734321347459</v>
+        <v>1.239599170131001</v>
       </c>
       <c r="F66">
-        <v>25.71044723176047</v>
+        <v>26.11217296975672</v>
       </c>
       <c r="G66">
         <v>0.5679999999999999</v>
@@ -6693,37 +6693,37 @@
         <v>2.8675</v>
       </c>
       <c r="M66">
-        <v>5.162657804137502</v>
+        <v>5.243324332327149</v>
       </c>
       <c r="N66">
-        <v>-2.295157804137502</v>
+        <v>-2.37582433232715</v>
       </c>
       <c r="O66">
-        <v>-0.5737894510343755</v>
+        <v>-0.5939560830817874</v>
       </c>
       <c r="P66">
-        <v>-1.721368353103127</v>
+        <v>-1.781868249245362</v>
       </c>
       <c r="Q66">
-        <v>-1.691368353103126</v>
+        <v>-1.751868249245362</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1142290636280612</v>
+        <v>0.11618417973172</v>
       </c>
       <c r="T66">
-        <v>1.333809817060065</v>
+        <v>1.371918668976066</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1388577409537924</v>
+        <v>0.1367214680160418</v>
       </c>
       <c r="W66">
-        <v>0.1729173656164785</v>
+        <v>0.1733463292223788</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5554309638151695</v>
+        <v>0.5468858720641672</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1533395769006483</v>
+        <v>0.1548895769006483</v>
       </c>
       <c r="C67">
-        <v>-12.40672976908935</v>
+        <v>-12.96438978428006</v>
       </c>
       <c r="D67">
-        <v>13.13744320066737</v>
+        <v>12.98150892347292</v>
       </c>
       <c r="E67">
-        <v>1.239599170131001</v>
+        <v>1.64132490812726</v>
       </c>
       <c r="F67">
-        <v>26.11217296975672</v>
+        <v>26.51389870775298</v>
       </c>
       <c r="G67">
         <v>0.5679999999999999</v>
@@ -6775,37 +6775,37 @@
         <v>2.8675</v>
       </c>
       <c r="M67">
-        <v>5.243324332327149</v>
+        <v>5.323990860516798</v>
       </c>
       <c r="N67">
-        <v>-2.37582433232715</v>
+        <v>-2.456490860516799</v>
       </c>
       <c r="O67">
-        <v>-0.5939560830817874</v>
+        <v>-0.6141227151291997</v>
       </c>
       <c r="P67">
-        <v>-1.781868249245362</v>
+        <v>-1.842368145387599</v>
       </c>
       <c r="Q67">
-        <v>-1.751868249245362</v>
+        <v>-1.812368145387599</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.11618417973172</v>
+        <v>0.1182543026650059</v>
       </c>
       <c r="T67">
-        <v>1.371918668976066</v>
+        <v>1.412269218063598</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1367214680160418</v>
+        <v>0.1346499306218593</v>
       </c>
       <c r="W67">
-        <v>0.1733463292223788</v>
+        <v>0.1737622939311307</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5468858720641672</v>
+        <v>0.5385997224874373</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1548895769006483</v>
+        <v>0.1564395769006482</v>
       </c>
       <c r="C68">
-        <v>-12.96438978428006</v>
+        <v>-13.51839151189944</v>
       </c>
       <c r="D68">
-        <v>12.98150892347292</v>
+        <v>12.8292329338498</v>
       </c>
       <c r="E68">
-        <v>1.64132490812726</v>
+        <v>2.043050646123518</v>
       </c>
       <c r="F68">
-        <v>26.51389870775298</v>
+        <v>26.91562444574924</v>
       </c>
       <c r="G68">
         <v>0.5679999999999999</v>
@@ -6857,37 +6857,37 @@
         <v>2.8675</v>
       </c>
       <c r="M68">
-        <v>5.323990860516798</v>
+        <v>5.404657388706447</v>
       </c>
       <c r="N68">
-        <v>-2.456490860516799</v>
+        <v>-2.537157388706447</v>
       </c>
       <c r="O68">
-        <v>-0.6141227151291997</v>
+        <v>-0.6342893471766118</v>
       </c>
       <c r="P68">
-        <v>-1.842368145387599</v>
+        <v>-1.902868041529835</v>
       </c>
       <c r="Q68">
-        <v>-1.812368145387599</v>
+        <v>-1.872868041529835</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1182543026650059</v>
+        <v>0.1204498875942485</v>
       </c>
       <c r="T68">
-        <v>1.412269218063598</v>
+        <v>1.455065254974616</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1346499306218593</v>
+        <v>0.1326402301648166</v>
       </c>
       <c r="W68">
-        <v>0.1737622939311307</v>
+        <v>0.1741658417829048</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5385997224874373</v>
+        <v>0.5305609206592665</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1564395769006482</v>
+        <v>0.1579895769006482</v>
       </c>
       <c r="C69">
-        <v>-13.51839151189944</v>
+        <v>-14.0688621969185</v>
       </c>
       <c r="D69">
-        <v>12.8292329338498</v>
+        <v>12.68048798682699</v>
       </c>
       <c r="E69">
-        <v>2.043050646123518</v>
+        <v>2.444776384119773</v>
       </c>
       <c r="F69">
-        <v>26.91562444574924</v>
+        <v>27.31735018374549</v>
       </c>
       <c r="G69">
         <v>0.5679999999999999</v>
@@ -6939,37 +6939,37 @@
         <v>2.8675</v>
       </c>
       <c r="M69">
-        <v>5.404657388706447</v>
+        <v>5.485323916896095</v>
       </c>
       <c r="N69">
-        <v>-2.537157388706447</v>
+        <v>-2.617823916896096</v>
       </c>
       <c r="O69">
-        <v>-0.6342893471766118</v>
+        <v>-0.6544559792240239</v>
       </c>
       <c r="P69">
-        <v>-1.902868041529835</v>
+        <v>-1.963367937672072</v>
       </c>
       <c r="Q69">
-        <v>-1.872868041529835</v>
+        <v>-1.933367937672071</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1204498875942485</v>
+        <v>0.1227826965815688</v>
       </c>
       <c r="T69">
-        <v>1.455065254974616</v>
+        <v>1.500536044192573</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1326402301648166</v>
+        <v>0.1306896385447458</v>
       </c>
       <c r="W69">
-        <v>0.1741658417829048</v>
+        <v>0.174557520580215</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5305609206592665</v>
+        <v>0.5227585541789832</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1579895769006482</v>
+        <v>0.1595395769006482</v>
       </c>
       <c r="C70">
-        <v>-14.0688621969185</v>
+        <v>-14.61592325071953</v>
       </c>
       <c r="D70">
-        <v>12.68048798682699</v>
+        <v>12.53515267102222</v>
       </c>
       <c r="E70">
-        <v>2.444776384119773</v>
+        <v>2.846502122116032</v>
       </c>
       <c r="F70">
-        <v>27.31735018374549</v>
+        <v>27.71907592174175</v>
       </c>
       <c r="G70">
         <v>0.5679999999999999</v>
@@ -7021,37 +7021,37 @@
         <v>2.8675</v>
       </c>
       <c r="M70">
-        <v>5.485323916896095</v>
+        <v>5.565990445085744</v>
       </c>
       <c r="N70">
-        <v>-2.617823916896096</v>
+        <v>-2.698490445085744</v>
       </c>
       <c r="O70">
-        <v>-0.6544559792240239</v>
+        <v>-0.674622611271436</v>
       </c>
       <c r="P70">
-        <v>-1.963367937672072</v>
+        <v>-2.023867833814308</v>
       </c>
       <c r="Q70">
-        <v>-1.933367937672071</v>
+        <v>-1.993867833814308</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1227826965815688</v>
+        <v>0.1252660093745226</v>
       </c>
       <c r="T70">
-        <v>1.500536044192573</v>
+        <v>1.548940432714914</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1306896385447458</v>
+        <v>0.1287955858122133</v>
       </c>
       <c r="W70">
-        <v>0.174557520580215</v>
+        <v>0.1749378463689076</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5227585541789832</v>
+        <v>0.515182343248853</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1595395769006482</v>
+        <v>0.1610895769006483</v>
       </c>
       <c r="C71">
-        <v>-14.61592325071953</v>
+        <v>-15.15969058161144</v>
       </c>
       <c r="D71">
-        <v>12.53515267102222</v>
+        <v>12.39311107812657</v>
       </c>
       <c r="E71">
-        <v>2.846502122116032</v>
+        <v>3.248227860112291</v>
       </c>
       <c r="F71">
-        <v>27.71907592174175</v>
+        <v>28.12080165973801</v>
       </c>
       <c r="G71">
         <v>0.5679999999999999</v>
@@ -7103,37 +7103,37 @@
         <v>2.8675</v>
       </c>
       <c r="M71">
-        <v>5.565990445085744</v>
+        <v>5.646656973275393</v>
       </c>
       <c r="N71">
-        <v>-2.698490445085744</v>
+        <v>-2.779156973275393</v>
       </c>
       <c r="O71">
-        <v>-0.674622611271436</v>
+        <v>-0.6947892433188483</v>
       </c>
       <c r="P71">
-        <v>-2.023867833814308</v>
+        <v>-2.084367729956545</v>
       </c>
       <c r="Q71">
-        <v>-1.993867833814308</v>
+        <v>-2.054367729956545</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1252660093745226</v>
+        <v>0.1279148763536734</v>
       </c>
       <c r="T71">
-        <v>1.548940432714914</v>
+        <v>1.600571780472078</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1287955858122133</v>
+        <v>0.1269556488720388</v>
       </c>
       <c r="W71">
-        <v>0.1749378463689076</v>
+        <v>0.1753073057064946</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.515182343248853</v>
+        <v>0.507822595488155</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1610895769006483</v>
+        <v>0.1626395769006483</v>
       </c>
       <c r="C72">
-        <v>-15.15969058161144</v>
+        <v>-15.70027490312568</v>
       </c>
       <c r="D72">
-        <v>12.39311107812657</v>
+        <v>12.25425249460859</v>
       </c>
       <c r="E72">
-        <v>3.248227860112291</v>
+        <v>3.649953598108546</v>
       </c>
       <c r="F72">
-        <v>28.12080165973801</v>
+        <v>28.52252739773427</v>
       </c>
       <c r="G72">
         <v>0.5679999999999999</v>
@@ -7185,37 +7185,37 @@
         <v>2.8675</v>
       </c>
       <c r="M72">
-        <v>5.646656973275393</v>
+        <v>5.72732350146504</v>
       </c>
       <c r="N72">
-        <v>-2.779156973275393</v>
+        <v>-2.859823501465041</v>
       </c>
       <c r="O72">
-        <v>-0.6947892433188483</v>
+        <v>-0.7149558753662602</v>
       </c>
       <c r="P72">
-        <v>-2.084367729956545</v>
+        <v>-2.14486762609878</v>
       </c>
       <c r="Q72">
-        <v>-2.054367729956545</v>
+        <v>-2.11486762609878</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1279148763536734</v>
+        <v>0.1307464238141449</v>
       </c>
       <c r="T72">
-        <v>1.600571780472078</v>
+        <v>1.655763910833184</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1269556488720388</v>
+        <v>0.1251675411414467</v>
       </c>
       <c r="W72">
-        <v>0.1753073057064946</v>
+        <v>0.1756663577387975</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.507822595488155</v>
+        <v>0.5006701645657867</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1626395769006483</v>
+        <v>0.1897462222507409</v>
       </c>
       <c r="C73">
-        <v>-15.70027490312568</v>
+        <v>-18.10976022620177</v>
       </c>
       <c r="D73">
-        <v>12.25425249460859</v>
+        <v>10.24649290952875</v>
       </c>
       <c r="E73">
-        <v>3.649953598108542</v>
+        <v>4.051679336104801</v>
       </c>
       <c r="F73">
-        <v>28.52252739773426</v>
+        <v>28.92425313573052</v>
       </c>
       <c r="G73">
         <v>0.5679999999999999</v>
@@ -7267,45 +7267,45 @@
         <v>2.8675</v>
       </c>
       <c r="M73">
-        <v>5.72732350146504</v>
+        <v>6.820338889405257</v>
       </c>
       <c r="N73">
-        <v>-2.859823501465041</v>
+        <v>-3.952838889405257</v>
       </c>
       <c r="O73">
-        <v>-0.7149558753662602</v>
+        <v>-0.9882097223513142</v>
       </c>
       <c r="P73">
-        <v>-2.14486762609878</v>
+        <v>-2.964629167053943</v>
       </c>
       <c r="Q73">
-        <v>-2.11486762609878</v>
+        <v>-2.934629167053942</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1307464238141449</v>
+        <v>0.135053958057838</v>
       </c>
       <c r="T73">
-        <v>1.655763910833183</v>
+        <v>1.739725770852035</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1251675411414467</v>
+        <v>0.1051084134710075</v>
       </c>
       <c r="W73">
-        <v>0.1756663577387975</v>
+        <v>0.2110154361035364</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5006701645657867</v>
+        <v>0.4204336538840301</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1897462222507409</v>
+        <v>0.1916462222507409</v>
       </c>
       <c r="C74">
-        <v>-18.10976022620177</v>
+        <v>-18.62782322364686</v>
       </c>
       <c r="D74">
-        <v>10.24649290952875</v>
+        <v>10.13015565007992</v>
       </c>
       <c r="E74">
-        <v>4.051679336104801</v>
+        <v>4.45340507410106</v>
       </c>
       <c r="F74">
-        <v>28.92425313573052</v>
+        <v>29.32597887372678</v>
       </c>
       <c r="G74">
         <v>0.5679999999999999</v>
@@ -7349,37 +7349,37 @@
         <v>2.8675</v>
       </c>
       <c r="M74">
-        <v>6.820338889405257</v>
+        <v>6.915065818424774</v>
       </c>
       <c r="N74">
-        <v>-3.952838889405257</v>
+        <v>-4.047565818424775</v>
       </c>
       <c r="O74">
-        <v>-0.9882097223513142</v>
+        <v>-1.011891454606194</v>
       </c>
       <c r="P74">
-        <v>-2.964629167053943</v>
+        <v>-3.035674363818581</v>
       </c>
       <c r="Q74">
-        <v>-2.934629167053942</v>
+        <v>-3.005674363818581</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.135053958057838</v>
+        <v>0.1383596602081283</v>
       </c>
       <c r="T74">
-        <v>1.739725770852035</v>
+        <v>1.804160058661369</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1051084134710075</v>
+        <v>0.1036685721905828</v>
       </c>
       <c r="W74">
-        <v>0.2110154361035364</v>
+        <v>0.2113549506774606</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4204336538840301</v>
+        <v>0.414674288762331</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1916462222507409</v>
+        <v>0.1935462222507409</v>
       </c>
       <c r="C75">
-        <v>-18.62782322364686</v>
+        <v>-19.1432741242583</v>
       </c>
       <c r="D75">
-        <v>10.13015565007992</v>
+        <v>10.01643048746473</v>
       </c>
       <c r="E75">
-        <v>4.45340507410106</v>
+        <v>4.855130812097315</v>
       </c>
       <c r="F75">
-        <v>29.32597887372678</v>
+        <v>29.72770461172303</v>
       </c>
       <c r="G75">
         <v>0.5679999999999999</v>
@@ -7431,37 +7431,37 @@
         <v>2.8675</v>
       </c>
       <c r="M75">
-        <v>6.915065818424774</v>
+        <v>7.009792747444291</v>
       </c>
       <c r="N75">
-        <v>-4.047565818424775</v>
+        <v>-4.142292747444292</v>
       </c>
       <c r="O75">
-        <v>-1.011891454606194</v>
+        <v>-1.035573186861073</v>
       </c>
       <c r="P75">
-        <v>-3.035674363818581</v>
+        <v>-3.106719560583219</v>
       </c>
       <c r="Q75">
-        <v>-3.005674363818581</v>
+        <v>-3.076719560583219</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1383596602081283</v>
+        <v>0.1419196471392102</v>
       </c>
       <c r="T75">
-        <v>1.804160058661369</v>
+        <v>1.873550830148345</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1036685721905828</v>
+        <v>0.1022676455393587</v>
       </c>
       <c r="W75">
-        <v>0.2113549506774606</v>
+        <v>0.2116852891818193</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.414674288762331</v>
+        <v>0.4090705821574346</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1935462222507409</v>
+        <v>0.1954462222507409</v>
       </c>
       <c r="C76">
-        <v>-19.1432741242583</v>
+        <v>-19.65619992469563</v>
       </c>
       <c r="D76">
-        <v>10.01643048746473</v>
+        <v>9.90523042502366</v>
       </c>
       <c r="E76">
-        <v>4.855130812097315</v>
+        <v>5.256856550093573</v>
       </c>
       <c r="F76">
-        <v>29.72770461172303</v>
+        <v>30.12943034971929</v>
       </c>
       <c r="G76">
         <v>0.5679999999999999</v>
@@ -7513,37 +7513,37 @@
         <v>2.8675</v>
       </c>
       <c r="M76">
-        <v>7.009792747444291</v>
+        <v>7.104519676463809</v>
       </c>
       <c r="N76">
-        <v>-4.142292747444292</v>
+        <v>-4.23701967646381</v>
       </c>
       <c r="O76">
-        <v>-1.035573186861073</v>
+        <v>-1.059254919115952</v>
       </c>
       <c r="P76">
-        <v>-3.106719560583219</v>
+        <v>-3.177764757347857</v>
       </c>
       <c r="Q76">
-        <v>-3.076719560583219</v>
+        <v>-3.147764757347857</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1419196471392102</v>
+        <v>0.1457644330247786</v>
       </c>
       <c r="T76">
-        <v>1.873550830148345</v>
+        <v>1.948492863354279</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1022676455393587</v>
+        <v>0.1009040769321672</v>
       </c>
       <c r="W76">
-        <v>0.2116852891818193</v>
+        <v>0.212006818659395</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4090705821574346</v>
+        <v>0.4036163077286689</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1954462222507409</v>
+        <v>0.1973462222507409</v>
       </c>
       <c r="C77">
-        <v>-19.65619992469563</v>
+        <v>-20.1666838007705</v>
       </c>
       <c r="D77">
-        <v>9.90523042502366</v>
+        <v>9.79647228694505</v>
       </c>
       <c r="E77">
-        <v>5.256856550093573</v>
+        <v>5.658582288089832</v>
       </c>
       <c r="F77">
-        <v>30.12943034971929</v>
+        <v>30.53115608771555</v>
       </c>
       <c r="G77">
         <v>0.5679999999999999</v>
@@ -7595,37 +7595,37 @@
         <v>2.8675</v>
       </c>
       <c r="M77">
-        <v>7.104519676463809</v>
+        <v>7.199246605483327</v>
       </c>
       <c r="N77">
-        <v>-4.23701967646381</v>
+        <v>-4.331746605483327</v>
       </c>
       <c r="O77">
-        <v>-1.059254919115952</v>
+        <v>-1.082936651370832</v>
       </c>
       <c r="P77">
-        <v>-3.177764757347857</v>
+        <v>-3.248809954112495</v>
       </c>
       <c r="Q77">
-        <v>-3.147764757347857</v>
+        <v>-3.218809954112495</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1457644330247786</v>
+        <v>0.1499296177341444</v>
       </c>
       <c r="T77">
-        <v>1.948492863354279</v>
+        <v>2.029680065994041</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1009040769321672</v>
+        <v>0.09957639170937553</v>
       </c>
       <c r="W77">
-        <v>0.212006818659395</v>
+        <v>0.2123198868349293</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4036163077286689</v>
+        <v>0.3983055668375022</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1973462222507409</v>
+        <v>0.1992462222507409</v>
       </c>
       <c r="C78">
-        <v>-20.1666838007705</v>
+        <v>-20.67480531493057</v>
       </c>
       <c r="D78">
-        <v>9.79647228694505</v>
+        <v>9.690076510781232</v>
       </c>
       <c r="E78">
-        <v>5.658582288089832</v>
+        <v>6.060308026086087</v>
       </c>
       <c r="F78">
-        <v>30.53115608771555</v>
+        <v>30.93288182571181</v>
       </c>
       <c r="G78">
         <v>0.5679999999999999</v>
@@ -7677,37 +7677,37 @@
         <v>2.8675</v>
       </c>
       <c r="M78">
-        <v>7.199246605483327</v>
+        <v>7.293973534502844</v>
       </c>
       <c r="N78">
-        <v>-4.331746605483327</v>
+        <v>-4.426473534502844</v>
       </c>
       <c r="O78">
-        <v>-1.082936651370832</v>
+        <v>-1.106618383625711</v>
       </c>
       <c r="P78">
-        <v>-3.248809954112495</v>
+        <v>-3.319855150877133</v>
       </c>
       <c r="Q78">
-        <v>-3.218809954112495</v>
+        <v>-3.289855150877133</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1499296177341444</v>
+        <v>0.1544569924182376</v>
       </c>
       <c r="T78">
-        <v>2.029680065994041</v>
+        <v>2.117927025385086</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09957639170937553</v>
+        <v>0.09828319181704599</v>
       </c>
       <c r="W78">
-        <v>0.2123198868349293</v>
+        <v>0.2126248233695406</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3983055668375022</v>
+        <v>0.3931327672681839</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1992462222507409</v>
+        <v>0.2011462222507409</v>
       </c>
       <c r="C79">
-        <v>-20.67480531493057</v>
+        <v>-21.18064061036829</v>
       </c>
       <c r="D79">
-        <v>9.690076510781232</v>
+        <v>9.585966953339781</v>
       </c>
       <c r="E79">
-        <v>6.060308026086087</v>
+        <v>6.462033764082346</v>
       </c>
       <c r="F79">
-        <v>30.93288182571181</v>
+        <v>31.33460756370807</v>
       </c>
       <c r="G79">
         <v>0.5679999999999999</v>
@@ -7759,37 +7759,37 @@
         <v>2.8675</v>
       </c>
       <c r="M79">
-        <v>7.293973534502844</v>
+        <v>7.388700463522362</v>
       </c>
       <c r="N79">
-        <v>-4.426473534502844</v>
+        <v>-4.521200463522362</v>
       </c>
       <c r="O79">
-        <v>-1.106618383625711</v>
+        <v>-1.130300115880591</v>
       </c>
       <c r="P79">
-        <v>-3.319855150877133</v>
+        <v>-3.390900347641772</v>
       </c>
       <c r="Q79">
-        <v>-3.289855150877133</v>
+        <v>-3.360900347641771</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1544569924182376</v>
+        <v>0.1593959466190666</v>
       </c>
       <c r="T79">
-        <v>2.117927025385086</v>
+        <v>2.214196435629863</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09828319181704599</v>
+        <v>0.09702315089631462</v>
       </c>
       <c r="W79">
-        <v>0.2126248233695406</v>
+        <v>0.212921941018649</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3931327672681839</v>
+        <v>0.3880926035852585</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2011462222507409</v>
+        <v>0.2030462222507409</v>
       </c>
       <c r="C80">
-        <v>-21.18064061036829</v>
+        <v>-21.68426259274963</v>
       </c>
       <c r="D80">
-        <v>9.585966953339781</v>
+        <v>9.484070708954699</v>
       </c>
       <c r="E80">
-        <v>6.462033764082346</v>
+        <v>6.863759502078604</v>
       </c>
       <c r="F80">
-        <v>31.33460756370807</v>
+        <v>31.73633330170432</v>
       </c>
       <c r="G80">
         <v>0.5679999999999999</v>
@@ -7841,37 +7841,37 @@
         <v>2.8675</v>
       </c>
       <c r="M80">
-        <v>7.388700463522362</v>
+        <v>7.48342739254188</v>
       </c>
       <c r="N80">
-        <v>-4.521200463522362</v>
+        <v>-4.61592739254188</v>
       </c>
       <c r="O80">
-        <v>-1.130300115880591</v>
+        <v>-1.15398184813547</v>
       </c>
       <c r="P80">
-        <v>-3.390900347641772</v>
+        <v>-3.46194554440641</v>
       </c>
       <c r="Q80">
-        <v>-3.360900347641771</v>
+        <v>-3.43194554440641</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1593959466190666</v>
+        <v>0.1648052774104508</v>
       </c>
       <c r="T80">
-        <v>2.214196435629863</v>
+        <v>2.319634361136047</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09702315089631462</v>
+        <v>0.09579500974572835</v>
       </c>
       <c r="W80">
-        <v>0.212921941018649</v>
+        <v>0.2132115367019573</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3880926035852585</v>
+        <v>0.3831800389829134</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2030462222507409</v>
+        <v>0.2049462222507409</v>
       </c>
       <c r="C81">
-        <v>-21.68426259274963</v>
+        <v>-22.1857411004745</v>
       </c>
       <c r="D81">
-        <v>9.484070708954699</v>
+        <v>9.384317939226076</v>
       </c>
       <c r="E81">
-        <v>6.863759502078604</v>
+        <v>7.26548524007486</v>
       </c>
       <c r="F81">
-        <v>31.73633330170432</v>
+        <v>32.13805903970058</v>
       </c>
       <c r="G81">
         <v>0.5679999999999999</v>
@@ -7923,37 +7923,37 @@
         <v>2.8675</v>
       </c>
       <c r="M81">
-        <v>7.48342739254188</v>
+        <v>7.578154321561397</v>
       </c>
       <c r="N81">
-        <v>-4.61592739254188</v>
+        <v>-4.710654321561397</v>
       </c>
       <c r="O81">
-        <v>-1.15398184813547</v>
+        <v>-1.177663580390349</v>
       </c>
       <c r="P81">
-        <v>-3.46194554440641</v>
+        <v>-3.532990741171048</v>
       </c>
       <c r="Q81">
-        <v>-3.43194554440641</v>
+        <v>-3.502990741171048</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1648052774104508</v>
+        <v>0.1707555412809733</v>
       </c>
       <c r="T81">
-        <v>2.319634361136047</v>
+        <v>2.435616079192849</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09579500974572835</v>
+        <v>0.09459757212390676</v>
       </c>
       <c r="W81">
-        <v>0.2132115367019573</v>
+        <v>0.2134938924931828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3831800389829134</v>
+        <v>0.3783902884956271</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2049462222507409</v>
+        <v>0.2068462222507409</v>
       </c>
       <c r="C82">
-        <v>-22.1857411004745</v>
+        <v>-22.68514306430421</v>
       </c>
       <c r="D82">
-        <v>9.384317939226076</v>
+        <v>9.286641713392623</v>
       </c>
       <c r="E82">
-        <v>7.26548524007486</v>
+        <v>7.667210978071118</v>
       </c>
       <c r="F82">
-        <v>32.13805903970058</v>
+        <v>32.53978477769684</v>
       </c>
       <c r="G82">
         <v>0.5679999999999999</v>
@@ -8005,37 +8005,37 @@
         <v>2.8675</v>
       </c>
       <c r="M82">
-        <v>7.578154321561397</v>
+        <v>7.672881250580915</v>
       </c>
       <c r="N82">
-        <v>-4.710654321561397</v>
+        <v>-4.805381250580915</v>
       </c>
       <c r="O82">
-        <v>-1.177663580390349</v>
+        <v>-1.201345312645229</v>
       </c>
       <c r="P82">
-        <v>-3.532990741171048</v>
+        <v>-3.604035937935686</v>
       </c>
       <c r="Q82">
-        <v>-3.502990741171048</v>
+        <v>-3.574035937935686</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1707555412809733</v>
+        <v>0.177332148716814</v>
       </c>
       <c r="T82">
-        <v>2.435616079192849</v>
+        <v>2.563806399150368</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09459757212390676</v>
+        <v>0.09342970086311779</v>
       </c>
       <c r="W82">
-        <v>0.2134938924931828</v>
+        <v>0.2137692765364768</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3783902884956271</v>
+        <v>0.3737188034524711</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2068462222507409</v>
+        <v>0.2087462222507409</v>
       </c>
       <c r="C83">
-        <v>-22.68514306430421</v>
+        <v>-23.18253265712272</v>
       </c>
       <c r="D83">
-        <v>9.286641713392623</v>
+        <v>9.190977858570372</v>
       </c>
       <c r="E83">
-        <v>7.667210978071118</v>
+        <v>8.068936716067377</v>
       </c>
       <c r="F83">
-        <v>32.53978477769684</v>
+        <v>32.9415105156931</v>
       </c>
       <c r="G83">
         <v>0.5679999999999999</v>
@@ -8087,37 +8087,37 @@
         <v>2.8675</v>
       </c>
       <c r="M83">
-        <v>7.672881250580915</v>
+        <v>7.767608179600432</v>
       </c>
       <c r="N83">
-        <v>-4.805381250580915</v>
+        <v>-4.900108179600433</v>
       </c>
       <c r="O83">
-        <v>-1.201345312645229</v>
+        <v>-1.225027044900108</v>
       </c>
       <c r="P83">
-        <v>-3.604035937935686</v>
+        <v>-3.675081134700324</v>
       </c>
       <c r="Q83">
-        <v>-3.574035937935686</v>
+        <v>-3.645081134700324</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.177332148716814</v>
+        <v>0.1846394903121926</v>
       </c>
       <c r="T83">
-        <v>2.563806399150368</v>
+        <v>2.706240087992055</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09342970086311779</v>
+        <v>0.0922903142672261</v>
       </c>
       <c r="W83">
-        <v>0.2137692765364768</v>
+        <v>0.2140379438957881</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3737188034524711</v>
+        <v>0.3691612570689043</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2087462222507409</v>
+        <v>0.2106462222507409</v>
       </c>
       <c r="C84">
-        <v>-23.18253265712272</v>
+        <v>-23.67797143453602</v>
       </c>
       <c r="D84">
-        <v>9.190977858570372</v>
+        <v>9.097264819153335</v>
       </c>
       <c r="E84">
-        <v>8.068936716067377</v>
+        <v>8.470662454063635</v>
       </c>
       <c r="F84">
-        <v>32.9415105156931</v>
+        <v>33.34323625368935</v>
       </c>
       <c r="G84">
         <v>0.5679999999999999</v>
@@ -8169,37 +8169,37 @@
         <v>2.8675</v>
       </c>
       <c r="M84">
-        <v>7.767608179600432</v>
+        <v>7.86233510861995</v>
       </c>
       <c r="N84">
-        <v>-4.900108179600433</v>
+        <v>-4.994835108619951</v>
       </c>
       <c r="O84">
-        <v>-1.225027044900108</v>
+        <v>-1.248708777154988</v>
       </c>
       <c r="P84">
-        <v>-3.675081134700324</v>
+        <v>-3.746126331464963</v>
       </c>
       <c r="Q84">
-        <v>-3.645081134700324</v>
+        <v>-3.716126331464963</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1846394903121926</v>
+        <v>0.1928065191540863</v>
       </c>
       <c r="T84">
-        <v>2.706240087992055</v>
+        <v>2.865430681403353</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0922903142672261</v>
+        <v>0.0911783827700306</v>
       </c>
       <c r="W84">
-        <v>0.2140379438957881</v>
+        <v>0.2143001373428268</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3691612570689043</v>
+        <v>0.3647135310801224</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2106462222507409</v>
+        <v>0.2125462222507409</v>
       </c>
       <c r="C85">
-        <v>-23.67797143453602</v>
+        <v>-24.17151846695678</v>
       </c>
       <c r="D85">
-        <v>9.097264819153335</v>
+        <v>9.00544352472884</v>
       </c>
       <c r="E85">
-        <v>8.470662454063635</v>
+        <v>8.872388192059894</v>
       </c>
       <c r="F85">
-        <v>33.34323625368935</v>
+        <v>33.74496199168561</v>
       </c>
       <c r="G85">
         <v>0.5679999999999999</v>
@@ -8251,37 +8251,37 @@
         <v>2.8675</v>
       </c>
       <c r="M85">
-        <v>7.86233510861995</v>
+        <v>7.957062037639468</v>
       </c>
       <c r="N85">
-        <v>-4.994835108619951</v>
+        <v>-5.089562037639468</v>
       </c>
       <c r="O85">
-        <v>-1.248708777154988</v>
+        <v>-1.272390509409867</v>
       </c>
       <c r="P85">
-        <v>-3.746126331464963</v>
+        <v>-3.817171528229601</v>
       </c>
       <c r="Q85">
-        <v>-3.716126331464963</v>
+        <v>-3.787171528229601</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1928065191540863</v>
+        <v>0.2019944266012167</v>
       </c>
       <c r="T85">
-        <v>2.865430681403353</v>
+        <v>3.044520098991063</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0911783827700306</v>
+        <v>0.09009292583229214</v>
       </c>
       <c r="W85">
-        <v>0.2143001373428268</v>
+        <v>0.2145560880887455</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3647135310801224</v>
+        <v>0.3603717033291686</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2125462222507409</v>
+        <v>0.2144462222507409</v>
       </c>
       <c r="C86">
-        <v>-24.17151846695676</v>
+        <v>-24.66323046376993</v>
       </c>
       <c r="D86">
-        <v>9.005443524728845</v>
+        <v>8.915457265911931</v>
       </c>
       <c r="E86">
-        <v>8.872388192059887</v>
+        <v>9.274113930056146</v>
       </c>
       <c r="F86">
-        <v>33.74496199168561</v>
+        <v>34.14668772968187</v>
       </c>
       <c r="G86">
         <v>0.5679999999999999</v>
@@ -8333,37 +8333,37 @@
         <v>2.8675</v>
       </c>
       <c r="M86">
-        <v>7.957062037639466</v>
+        <v>8.051788966658984</v>
       </c>
       <c r="N86">
-        <v>-5.089562037639467</v>
+        <v>-5.184288966658984</v>
       </c>
       <c r="O86">
-        <v>-1.272390509409867</v>
+        <v>-1.296072241664746</v>
       </c>
       <c r="P86">
-        <v>-3.8171715282296</v>
+        <v>-3.888216724994238</v>
       </c>
       <c r="Q86">
-        <v>-3.787171528229599</v>
+        <v>-3.858216724994238</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2019944266012166</v>
+        <v>0.212407388374631</v>
       </c>
       <c r="T86">
-        <v>3.044520098991061</v>
+        <v>3.247488105590465</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09009292583229216</v>
+        <v>0.0890330090577946</v>
       </c>
       <c r="W86">
-        <v>0.2145560880887455</v>
+        <v>0.214806016464172</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3603717033291686</v>
+        <v>0.3561320362311784</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2144462222507409</v>
+        <v>0.2163462222507409</v>
       </c>
       <c r="C87">
-        <v>-24.66323046376993</v>
+        <v>-25.15316189012771</v>
       </c>
       <c r="D87">
-        <v>8.915457265911931</v>
+        <v>8.827251577550417</v>
       </c>
       <c r="E87">
-        <v>9.274113930056146</v>
+        <v>9.675839668052404</v>
       </c>
       <c r="F87">
-        <v>34.14668772968187</v>
+        <v>34.54841346767812</v>
       </c>
       <c r="G87">
         <v>0.5679999999999999</v>
@@ -8415,37 +8415,37 @@
         <v>2.8675</v>
       </c>
       <c r="M87">
-        <v>8.051788966658984</v>
+        <v>8.146515895678501</v>
       </c>
       <c r="N87">
-        <v>-5.184288966658984</v>
+        <v>-5.279015895678501</v>
       </c>
       <c r="O87">
-        <v>-1.296072241664746</v>
+        <v>-1.319753973919625</v>
       </c>
       <c r="P87">
-        <v>-3.888216724994238</v>
+        <v>-3.959261921758876</v>
       </c>
       <c r="Q87">
-        <v>-3.858216724994238</v>
+        <v>-3.929261921758876</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.212407388374631</v>
+        <v>0.2243079161156761</v>
       </c>
       <c r="T87">
-        <v>3.247488105590465</v>
+        <v>3.479451541704069</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0890330090577946</v>
+        <v>0.08799774151061095</v>
       </c>
       <c r="W87">
-        <v>0.214806016464172</v>
+        <v>0.2150501325517979</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3561320362311784</v>
+        <v>0.3519909660424437</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2163462222507409</v>
+        <v>0.2182462222507409</v>
       </c>
       <c r="C88">
-        <v>-25.15316189012771</v>
+        <v>-25.64136507687926</v>
       </c>
       <c r="D88">
-        <v>8.827251577550417</v>
+        <v>8.740774128795126</v>
       </c>
       <c r="E88">
-        <v>9.675839668052404</v>
+        <v>10.07756540604866</v>
       </c>
       <c r="F88">
-        <v>34.54841346767812</v>
+        <v>34.95013920567438</v>
       </c>
       <c r="G88">
         <v>0.5679999999999999</v>
@@ -8497,37 +8497,37 @@
         <v>2.8675</v>
       </c>
       <c r="M88">
-        <v>8.146515895678501</v>
+        <v>8.24124282469802</v>
       </c>
       <c r="N88">
-        <v>-5.279015895678501</v>
+        <v>-5.37374282469802</v>
       </c>
       <c r="O88">
-        <v>-1.319753973919625</v>
+        <v>-1.343435706174505</v>
       </c>
       <c r="P88">
-        <v>-3.959261921758876</v>
+        <v>-4.030307118523515</v>
       </c>
       <c r="Q88">
-        <v>-3.929261921758876</v>
+        <v>-4.000307118523515</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2243079161156761</v>
+        <v>0.2380392942784204</v>
       </c>
       <c r="T88">
-        <v>3.479451541704069</v>
+        <v>3.74710166029669</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08799774151061095</v>
+        <v>0.08698627321738552</v>
       </c>
       <c r="W88">
-        <v>0.2150501325517979</v>
+        <v>0.2152886367753405</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3519909660424437</v>
+        <v>0.3479450928695421</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2182462222507409</v>
+        <v>0.2201462222507409</v>
       </c>
       <c r="C89">
-        <v>-25.64136507687926</v>
+        <v>-26.12789032410153</v>
       </c>
       <c r="D89">
-        <v>8.740774128795126</v>
+        <v>8.655974619569108</v>
       </c>
       <c r="E89">
-        <v>10.07756540604866</v>
+        <v>10.47929114404491</v>
       </c>
       <c r="F89">
-        <v>34.95013920567438</v>
+        <v>35.35186494367063</v>
       </c>
       <c r="G89">
         <v>0.5679999999999999</v>
@@ -8579,37 +8579,37 @@
         <v>2.8675</v>
       </c>
       <c r="M89">
-        <v>8.24124282469802</v>
+        <v>8.335969753717535</v>
       </c>
       <c r="N89">
-        <v>-5.37374282469802</v>
+        <v>-5.468469753717535</v>
       </c>
       <c r="O89">
-        <v>-1.343435706174505</v>
+        <v>-1.367117438429384</v>
       </c>
       <c r="P89">
-        <v>-4.030307118523515</v>
+        <v>-4.101352315288151</v>
       </c>
       <c r="Q89">
-        <v>-4.000307118523515</v>
+        <v>-4.071352315288151</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2380392942784204</v>
+        <v>0.2540592354682888</v>
       </c>
       <c r="T89">
-        <v>3.74710166029669</v>
+        <v>4.059360131988082</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08698627321738552</v>
+        <v>0.08599779283991525</v>
       </c>
       <c r="W89">
-        <v>0.2152886367753405</v>
+        <v>0.215521720448348</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3479450928695421</v>
+        <v>0.343991171359661</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2201462222507409</v>
+        <v>0.2220462222507409</v>
       </c>
       <c r="C90">
-        <v>-26.12789032410153</v>
+        <v>-26.61278599866147</v>
       </c>
       <c r="D90">
-        <v>8.655974619569108</v>
+        <v>8.572804683005426</v>
       </c>
       <c r="E90">
-        <v>10.47929114404491</v>
+        <v>10.88101688204117</v>
       </c>
       <c r="F90">
-        <v>35.35186494367063</v>
+        <v>35.75359068166689</v>
       </c>
       <c r="G90">
         <v>0.5679999999999999</v>
@@ -8661,37 +8661,37 @@
         <v>2.8675</v>
       </c>
       <c r="M90">
-        <v>8.335969753717535</v>
+        <v>8.430696682737054</v>
       </c>
       <c r="N90">
-        <v>-5.468469753717535</v>
+        <v>-5.563196682737054</v>
       </c>
       <c r="O90">
-        <v>-1.367117438429384</v>
+        <v>-1.390799170684264</v>
       </c>
       <c r="P90">
-        <v>-4.101352315288151</v>
+        <v>-4.172397512052791</v>
       </c>
       <c r="Q90">
-        <v>-4.071352315288151</v>
+        <v>-4.14239751205279</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2540592354682888</v>
+        <v>0.2729918932381332</v>
       </c>
       <c r="T90">
-        <v>4.059360131988082</v>
+        <v>4.428392871259725</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08599779283991525</v>
+        <v>0.08503152550463529</v>
       </c>
       <c r="W90">
-        <v>0.215521720448348</v>
+        <v>0.215749566286007</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.343991171359661</v>
+        <v>0.3401261020185412</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2220462222507409</v>
+        <v>0.2239462222507409</v>
       </c>
       <c r="C91">
-        <v>-26.61278599866147</v>
+        <v>-27.09609862620723</v>
       </c>
       <c r="D91">
-        <v>8.572804683005426</v>
+        <v>8.491217793455919</v>
       </c>
       <c r="E91">
-        <v>10.88101688204117</v>
+        <v>11.28274262003743</v>
       </c>
       <c r="F91">
-        <v>35.75359068166689</v>
+        <v>36.15531641966315</v>
       </c>
       <c r="G91">
         <v>0.5679999999999999</v>
@@ -8743,37 +8743,37 @@
         <v>2.8675</v>
       </c>
       <c r="M91">
-        <v>8.430696682737054</v>
+        <v>8.525423611756571</v>
       </c>
       <c r="N91">
-        <v>-5.563196682737054</v>
+        <v>-5.657923611756571</v>
       </c>
       <c r="O91">
-        <v>-1.390799170684264</v>
+        <v>-1.414480902939143</v>
       </c>
       <c r="P91">
-        <v>-4.172397512052791</v>
+        <v>-4.243442708817428</v>
       </c>
       <c r="Q91">
-        <v>-4.14239751205279</v>
+        <v>-4.213442708817428</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2729918932381332</v>
+        <v>0.2957110825619466</v>
       </c>
       <c r="T91">
-        <v>4.428392871259725</v>
+        <v>4.871232158385698</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08503152550463529</v>
+        <v>0.08408673077680602</v>
       </c>
       <c r="W91">
-        <v>0.215749566286007</v>
+        <v>0.2159723488828292</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3401261020185412</v>
+        <v>0.336346923107224</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2239462222507409</v>
+        <v>0.2258462222507409</v>
       </c>
       <c r="C92">
-        <v>-27.09609862620723</v>
+        <v>-27.57787297795613</v>
       </c>
       <c r="D92">
-        <v>8.491217793455919</v>
+        <v>8.411169179703279</v>
       </c>
       <c r="E92">
-        <v>11.28274262003743</v>
+        <v>11.68446835803369</v>
       </c>
       <c r="F92">
-        <v>36.15531641966315</v>
+        <v>36.55704215765941</v>
       </c>
       <c r="G92">
         <v>0.5679999999999999</v>
@@ -8825,37 +8825,37 @@
         <v>2.8675</v>
       </c>
       <c r="M92">
-        <v>8.525423611756571</v>
+        <v>8.620150540776089</v>
       </c>
       <c r="N92">
-        <v>-5.657923611756571</v>
+        <v>-5.75265054077609</v>
       </c>
       <c r="O92">
-        <v>-1.414480902939143</v>
+        <v>-1.438162635194022</v>
       </c>
       <c r="P92">
-        <v>-4.243442708817428</v>
+        <v>-4.314487905582068</v>
       </c>
       <c r="Q92">
-        <v>-4.213442708817428</v>
+        <v>-4.284487905582067</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2957110825619466</v>
+        <v>0.3234789806243851</v>
       </c>
       <c r="T92">
-        <v>4.871232158385698</v>
+        <v>5.412480175984109</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08408673077680602</v>
+        <v>0.08316270076826968</v>
       </c>
       <c r="W92">
-        <v>0.2159723488828292</v>
+        <v>0.216190235158842</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.336346923107224</v>
+        <v>0.3326508030730787</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2258462222507409</v>
+        <v>0.2277462222507409</v>
       </c>
       <c r="C93">
-        <v>-27.57787297795613</v>
+        <v>-28.05815215261933</v>
       </c>
       <c r="D93">
-        <v>8.411169179703279</v>
+        <v>8.332615743036337</v>
       </c>
       <c r="E93">
-        <v>11.68446835803369</v>
+        <v>12.08619409602995</v>
       </c>
       <c r="F93">
-        <v>36.55704215765941</v>
+        <v>36.95876789565567</v>
       </c>
       <c r="G93">
         <v>0.5679999999999999</v>
@@ -8907,37 +8907,37 @@
         <v>2.8675</v>
       </c>
       <c r="M93">
-        <v>8.620150540776089</v>
+        <v>8.714877469795606</v>
       </c>
       <c r="N93">
-        <v>-5.75265054077609</v>
+        <v>-5.847377469795607</v>
       </c>
       <c r="O93">
-        <v>-1.438162635194022</v>
+        <v>-1.461844367448902</v>
       </c>
       <c r="P93">
-        <v>-4.314487905582068</v>
+        <v>-4.385533102346705</v>
       </c>
       <c r="Q93">
-        <v>-4.284487905582067</v>
+        <v>-4.355533102346705</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3234789806243851</v>
+        <v>0.3581888532024334</v>
       </c>
       <c r="T93">
-        <v>5.412480175984109</v>
+        <v>6.089040197982126</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08316270076826968</v>
+        <v>0.08225875836861457</v>
       </c>
       <c r="W93">
-        <v>0.216190235158842</v>
+        <v>0.2164033847766807</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3326508030730787</v>
+        <v>0.3290350334744583</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2277462222507409</v>
+        <v>0.2296462222507409</v>
       </c>
       <c r="C94">
-        <v>-28.05815215261933</v>
+        <v>-28.53697765377846</v>
       </c>
       <c r="D94">
-        <v>8.332615743036337</v>
+        <v>8.255515979873469</v>
       </c>
       <c r="E94">
-        <v>12.08619409602995</v>
+        <v>12.48791983402621</v>
       </c>
       <c r="F94">
-        <v>36.95876789565567</v>
+        <v>37.36049363365193</v>
       </c>
       <c r="G94">
         <v>0.5679999999999999</v>
@@ -8989,37 +8989,37 @@
         <v>2.8675</v>
       </c>
       <c r="M94">
-        <v>8.714877469795606</v>
+        <v>8.809604398815125</v>
       </c>
       <c r="N94">
-        <v>-5.847377469795607</v>
+        <v>-5.942104398815125</v>
       </c>
       <c r="O94">
-        <v>-1.461844367448902</v>
+        <v>-1.485526099703781</v>
       </c>
       <c r="P94">
-        <v>-4.385533102346705</v>
+        <v>-4.456578299111344</v>
       </c>
       <c r="Q94">
-        <v>-4.355533102346705</v>
+        <v>-4.426578299111344</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3581888532024334</v>
+        <v>0.4028158322313525</v>
       </c>
       <c r="T94">
-        <v>6.089040197982126</v>
+        <v>6.958903083408144</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08225875836861457</v>
+        <v>0.08137425559045741</v>
       </c>
       <c r="W94">
-        <v>0.2164033847766807</v>
+        <v>0.2166119505317702</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3290350334744583</v>
+        <v>0.3254970223618296</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2296462222507409</v>
+        <v>0.2315462222507409</v>
       </c>
       <c r="C95">
-        <v>-28.53697765377846</v>
+        <v>-29.01438946300582</v>
       </c>
       <c r="D95">
-        <v>8.255515979873469</v>
+        <v>8.179829908642368</v>
       </c>
       <c r="E95">
-        <v>12.48791983402621</v>
+        <v>12.88964557202247</v>
       </c>
       <c r="F95">
-        <v>37.36049363365193</v>
+        <v>37.76221937164819</v>
       </c>
       <c r="G95">
         <v>0.5679999999999999</v>
@@ -9071,37 +9071,37 @@
         <v>2.8675</v>
       </c>
       <c r="M95">
-        <v>8.809604398815125</v>
+        <v>8.904331327834642</v>
       </c>
       <c r="N95">
-        <v>-5.942104398815125</v>
+        <v>-6.036831327834642</v>
       </c>
       <c r="O95">
-        <v>-1.485526099703781</v>
+        <v>-1.509207831958661</v>
       </c>
       <c r="P95">
-        <v>-4.456578299111344</v>
+        <v>-4.527623495875982</v>
       </c>
       <c r="Q95">
-        <v>-4.426578299111344</v>
+        <v>-4.497623495875982</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4028158322313525</v>
+        <v>0.462318470936578</v>
       </c>
       <c r="T95">
-        <v>6.958903083408144</v>
+        <v>8.11872026397617</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08137425559045741</v>
+        <v>0.08050857202034617</v>
       </c>
       <c r="W95">
-        <v>0.2166119505317702</v>
+        <v>0.2168160787176024</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3254970223618296</v>
+        <v>0.3220342880813847</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2315462222507409</v>
+        <v>0.2334462222507409</v>
       </c>
       <c r="C96">
-        <v>-29.01438946300582</v>
+        <v>-29.49042610899905</v>
       </c>
       <c r="D96">
-        <v>8.179829908642368</v>
+        <v>8.105519000645394</v>
       </c>
       <c r="E96">
-        <v>12.88964557202247</v>
+        <v>13.29137131001872</v>
       </c>
       <c r="F96">
-        <v>37.76221937164819</v>
+        <v>38.16394510964444</v>
       </c>
       <c r="G96">
         <v>0.5679999999999999</v>
@@ -9153,37 +9153,37 @@
         <v>2.8675</v>
       </c>
       <c r="M96">
-        <v>8.904331327834642</v>
+        <v>8.999058256854159</v>
       </c>
       <c r="N96">
-        <v>-6.036831327834642</v>
+        <v>-6.131558256854159</v>
       </c>
       <c r="O96">
-        <v>-1.509207831958661</v>
+        <v>-1.53288956421354</v>
       </c>
       <c r="P96">
-        <v>-4.527623495875982</v>
+        <v>-4.59866869264062</v>
       </c>
       <c r="Q96">
-        <v>-4.497623495875982</v>
+        <v>-4.568668692640619</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.462318470936578</v>
+        <v>0.5456221651238937</v>
       </c>
       <c r="T96">
-        <v>8.11872026397617</v>
+        <v>9.742464316771407</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08050857202034617</v>
+        <v>0.07966111336750042</v>
       </c>
       <c r="W96">
-        <v>0.2168160787176024</v>
+        <v>0.2170159094679434</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3220342880813847</v>
+        <v>0.3186444534700017</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2334462222507409</v>
+        <v>0.2353462222507409</v>
       </c>
       <c r="C97">
-        <v>-29.49042610899905</v>
+        <v>-29.96512473298126</v>
       </c>
       <c r="D97">
-        <v>8.105519000645394</v>
+        <v>8.032546114659439</v>
       </c>
       <c r="E97">
-        <v>13.29137131001872</v>
+        <v>13.69309704801498</v>
       </c>
       <c r="F97">
-        <v>38.16394510964444</v>
+        <v>38.5656708476407</v>
       </c>
       <c r="G97">
         <v>0.5679999999999999</v>
@@ -9235,37 +9235,37 @@
         <v>2.8675</v>
       </c>
       <c r="M97">
-        <v>8.999058256854159</v>
+        <v>9.093785185873676</v>
       </c>
       <c r="N97">
-        <v>-6.131558256854159</v>
+        <v>-6.226285185873676</v>
       </c>
       <c r="O97">
-        <v>-1.53288956421354</v>
+        <v>-1.556571296468419</v>
       </c>
       <c r="P97">
-        <v>-4.59866869264062</v>
+        <v>-4.669713889405257</v>
       </c>
       <c r="Q97">
-        <v>-4.568668692640619</v>
+        <v>-4.639713889405257</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5456221651238937</v>
+        <v>0.6705777064048675</v>
       </c>
       <c r="T97">
-        <v>9.742464316771407</v>
+        <v>12.17808039596427</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07966111336750042</v>
+        <v>0.07883131010325563</v>
       </c>
       <c r="W97">
-        <v>0.2170159094679434</v>
+        <v>0.2172115770776523</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3186444534700017</v>
+        <v>0.3153252404130226</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2353462222507409</v>
+        <v>0.2372462222507409</v>
       </c>
       <c r="C98">
-        <v>-29.96512473298126</v>
+        <v>-30.43852115060001</v>
       </c>
       <c r="D98">
-        <v>8.032546114659439</v>
+        <v>7.960875435036939</v>
       </c>
       <c r="E98">
-        <v>13.69309704801498</v>
+        <v>14.09482278601123</v>
       </c>
       <c r="F98">
-        <v>38.5656708476407</v>
+        <v>38.96739658563695</v>
       </c>
       <c r="G98">
         <v>0.5679999999999999</v>
@@ -9317,37 +9317,37 @@
         <v>2.8675</v>
       </c>
       <c r="M98">
-        <v>9.093785185873676</v>
+        <v>9.188512114893193</v>
       </c>
       <c r="N98">
-        <v>-6.226285185873676</v>
+        <v>-6.321012114893193</v>
       </c>
       <c r="O98">
-        <v>-1.556571296468419</v>
+        <v>-1.580253028723298</v>
       </c>
       <c r="P98">
-        <v>-4.669713889405257</v>
+        <v>-4.740759086169895</v>
       </c>
       <c r="Q98">
-        <v>-4.639713889405257</v>
+        <v>-4.710759086169895</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6705777064048657</v>
+        <v>0.8788369418731545</v>
       </c>
       <c r="T98">
-        <v>12.17808039596423</v>
+        <v>16.23744052795231</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07883131010325563</v>
+        <v>0.07801861618466538</v>
       </c>
       <c r="W98">
-        <v>0.2172115770776523</v>
+        <v>0.2174032103036559</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3153252404130226</v>
+        <v>0.3120744647386615</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2372462222507409</v>
+        <v>0.2391462222507409</v>
       </c>
       <c r="C99">
-        <v>-30.43852115060001</v>
+        <v>-30.9106499105418</v>
       </c>
       <c r="D99">
-        <v>7.960875435036939</v>
+        <v>7.890472413091405</v>
       </c>
       <c r="E99">
-        <v>14.09482278601123</v>
+        <v>14.49654852400749</v>
       </c>
       <c r="F99">
-        <v>38.96739658563695</v>
+        <v>39.36912232363321</v>
       </c>
       <c r="G99">
         <v>0.5679999999999999</v>
@@ -9399,37 +9399,37 @@
         <v>2.8675</v>
       </c>
       <c r="M99">
-        <v>9.188512114893193</v>
+        <v>9.28323904391271</v>
       </c>
       <c r="N99">
-        <v>-6.321012114893193</v>
+        <v>-6.41573904391271</v>
       </c>
       <c r="O99">
-        <v>-1.580253028723298</v>
+        <v>-1.603934760978178</v>
       </c>
       <c r="P99">
-        <v>-4.740759086169895</v>
+        <v>-4.811804282934533</v>
       </c>
       <c r="Q99">
-        <v>-4.710759086169895</v>
+        <v>-4.781804282934533</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8788369418731545</v>
+        <v>1.295355412809732</v>
       </c>
       <c r="T99">
-        <v>16.23744052795231</v>
+        <v>24.35616079192846</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07801861618466538</v>
+        <v>0.07722250785625043</v>
       </c>
       <c r="W99">
-        <v>0.2174032103036559</v>
+        <v>0.2175909326474962</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3120744647386615</v>
+        <v>0.3088900314250017</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2391462222507409</v>
+        <v>0.2410462222507409</v>
       </c>
       <c r="C100">
-        <v>-30.9106499105418</v>
+        <v>-31.3815443500636</v>
       </c>
       <c r="D100">
-        <v>7.890472413091405</v>
+        <v>7.821303711565866</v>
       </c>
       <c r="E100">
-        <v>14.49654852400749</v>
+        <v>14.89827426200375</v>
       </c>
       <c r="F100">
-        <v>39.36912232363321</v>
+        <v>39.77084806162947</v>
       </c>
       <c r="G100">
         <v>0.5679999999999999</v>
@@ -9481,37 +9481,37 @@
         <v>2.8675</v>
       </c>
       <c r="M100">
-        <v>9.28323904391271</v>
+        <v>9.377965972932229</v>
       </c>
       <c r="N100">
-        <v>-6.41573904391271</v>
+        <v>-6.510465972932229</v>
       </c>
       <c r="O100">
-        <v>-1.603934760978178</v>
+        <v>-1.627616493233057</v>
       </c>
       <c r="P100">
-        <v>-4.811804282934533</v>
+        <v>-4.882849479699171</v>
       </c>
       <c r="Q100">
-        <v>-4.781804282934533</v>
+        <v>-4.852849479699171</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.295355412809732</v>
+        <v>2.544910825619463</v>
       </c>
       <c r="T100">
-        <v>24.35616079192846</v>
+        <v>48.71232158385693</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07722250785625043</v>
+        <v>0.0764424825243691</v>
       </c>
       <c r="W100">
-        <v>0.2175909326474962</v>
+        <v>0.2177748626207538</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3088900314250017</v>
+        <v>0.3057699300974764</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2410462222507409</v>
-      </c>
-      <c r="C101">
-        <v>-31.3815443500636</v>
-      </c>
-      <c r="D101">
-        <v>7.821303711565866</v>
-      </c>
-      <c r="E101">
-        <v>14.89827426200375</v>
-      </c>
-      <c r="F101">
-        <v>39.77084806162947</v>
-      </c>
-      <c r="G101">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="H101">
-        <v>15.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.8975</v>
-      </c>
-      <c r="K101">
-        <v>0.03000000000000025</v>
-      </c>
-      <c r="L101">
-        <v>2.8675</v>
-      </c>
-      <c r="M101">
-        <v>9.377965972932229</v>
-      </c>
-      <c r="N101">
-        <v>-6.510465972932229</v>
-      </c>
-      <c r="O101">
-        <v>-1.627616493233057</v>
-      </c>
-      <c r="P101">
-        <v>-4.882849479699171</v>
-      </c>
-      <c r="Q101">
-        <v>-4.852849479699171</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.544910825619463</v>
-      </c>
-      <c r="T101">
-        <v>48.71232158385693</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0764424825243691</v>
-      </c>
-      <c r="W101">
-        <v>0.2177748626207538</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3057699300974764</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
